--- a/database/event/6865/event_6865_evp_summary.xlsx
+++ b/database/event/6865/event_6865_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>7.8843</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>4.3151</v>
       </c>
       <c r="D2" t="n">
         <v>2.7637</v>
@@ -545,7 +545,7 @@
         <v>6.6184</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>3.6222</v>
       </c>
       <c r="D3" t="n">
         <v>2.2523</v>
@@ -591,7 +591,7 @@
         <v>6.4982</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>3.5564</v>
       </c>
       <c r="D4" t="n">
         <v>2.2038</v>
@@ -637,7 +637,7 @@
         <v>6.3745</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>3.4887</v>
       </c>
       <c r="D5" t="n">
         <v>2.1538</v>
@@ -683,7 +683,7 @@
         <v>5.5022</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>3.0113</v>
       </c>
       <c r="D6" t="n">
         <v>1.8014</v>
@@ -729,7 +729,7 @@
         <v>5.4332</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>2.9736</v>
       </c>
       <c r="D7" t="n">
         <v>1.7735</v>
@@ -775,7 +775,7 @@
         <v>4.7116</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2.5786</v>
       </c>
       <c r="D8" t="n">
         <v>1.482</v>
@@ -821,7 +821,7 @@
         <v>4.3935</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2.4045</v>
       </c>
       <c r="D9" t="n">
         <v>1.3535</v>
@@ -867,7 +867,7 @@
         <v>4.1206</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>2.2552</v>
       </c>
       <c r="D10" t="n">
         <v>1.2433</v>
@@ -913,7 +913,7 @@
         <v>4.0563</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="D11" t="n">
         <v>1.2173</v>
@@ -959,7 +959,7 @@
         <v>3.1966</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1.7495</v>
       </c>
       <c r="D12" t="n">
         <v>0.87</v>
@@ -1005,7 +1005,7 @@
         <v>3.1023</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1.6979</v>
       </c>
       <c r="D13" t="n">
         <v>0.8319</v>
@@ -1051,7 +1051,7 @@
         <v>3.0988</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1.696</v>
       </c>
       <c r="D14" t="n">
         <v>0.8305</v>
@@ -1097,7 +1097,7 @@
         <v>2.9851</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1.6337</v>
       </c>
       <c r="D15" t="n">
         <v>0.7846</v>
@@ -1143,7 +1143,7 @@
         <v>2.9575</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1.6186</v>
       </c>
       <c r="D16" t="n">
         <v>0.7734</v>
@@ -1189,7 +1189,7 @@
         <v>2.544</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1.3923</v>
       </c>
       <c r="D17" t="n">
         <v>0.6064000000000001</v>
@@ -1235,7 +1235,7 @@
         <v>2.5021</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1.3694</v>
       </c>
       <c r="D18" t="n">
         <v>0.5894</v>
@@ -1281,7 +1281,7 @@
         <v>2.4401</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1.3355</v>
       </c>
       <c r="D19" t="n">
         <v>0.5644</v>
@@ -1327,7 +1327,7 @@
         <v>2.4218</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1.3254</v>
       </c>
       <c r="D20" t="n">
         <v>0.5570000000000001</v>
@@ -1373,7 +1373,7 @@
         <v>2.2581</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1.2359</v>
       </c>
       <c r="D21" t="n">
         <v>0.4909</v>
@@ -1419,7 +1419,7 @@
         <v>2.103</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1.151</v>
       </c>
       <c r="D22" t="n">
         <v>0.4282</v>
@@ -1465,7 +1465,7 @@
         <v>2.0998</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1.1492</v>
       </c>
       <c r="D23" t="n">
         <v>0.4269</v>
@@ -1511,7 +1511,7 @@
         <v>2.0838</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1.1405</v>
       </c>
       <c r="D24" t="n">
         <v>0.4204</v>
@@ -1557,7 +1557,7 @@
         <v>1.886</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1.0322</v>
       </c>
       <c r="D25" t="n">
         <v>0.3405</v>
@@ -1603,7 +1603,7 @@
         <v>1.7342</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.9491000000000001</v>
       </c>
       <c r="D26" t="n">
         <v>0.2792</v>
@@ -1649,7 +1649,7 @@
         <v>1.72</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.9414</v>
       </c>
       <c r="D27" t="n">
         <v>0.2735</v>
@@ -1695,7 +1695,7 @@
         <v>1.6691</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.9135</v>
       </c>
       <c r="D28" t="n">
         <v>0.2529</v>
@@ -1741,7 +1741,7 @@
         <v>1.5237</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.8339</v>
       </c>
       <c r="D29" t="n">
         <v>0.1942</v>
@@ -1787,7 +1787,7 @@
         <v>1.4499</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.7935</v>
       </c>
       <c r="D30" t="n">
         <v>0.1644</v>
@@ -1833,7 +1833,7 @@
         <v>1.3905</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.761</v>
       </c>
       <c r="D31" t="n">
         <v>0.1404</v>
@@ -1879,7 +1879,7 @@
         <v>1.2126</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.6637</v>
       </c>
       <c r="D32" t="n">
         <v>0.06850000000000001</v>
@@ -1925,7 +1925,7 @@
         <v>1.1817</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="D33" t="n">
         <v>0.056</v>
@@ -1971,7 +1971,7 @@
         <v>1.1572</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.6333</v>
       </c>
       <c r="D34" t="n">
         <v>0.0461</v>
@@ -2017,7 +2017,7 @@
         <v>1.0656</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="D35" t="n">
         <v>0.0091</v>
@@ -2063,7 +2063,7 @@
         <v>1.0088</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.5521</v>
       </c>
       <c r="D36" t="n">
         <v>-0.0138</v>
@@ -2109,7 +2109,7 @@
         <v>0.9857</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.5395</v>
       </c>
       <c r="D37" t="n">
         <v>-0.0232</v>
@@ -2155,7 +2155,7 @@
         <v>0.9719</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.5319</v>
       </c>
       <c r="D38" t="n">
         <v>-0.0287</v>
@@ -2201,7 +2201,7 @@
         <v>0.9423</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.5157</v>
       </c>
       <c r="D39" t="n">
         <v>-0.0407</v>
@@ -2247,7 +2247,7 @@
         <v>0.8275</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.4529</v>
       </c>
       <c r="D40" t="n">
         <v>-0.0871</v>
@@ -2293,7 +2293,7 @@
         <v>0.8186</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.448</v>
       </c>
       <c r="D41" t="n">
         <v>-0.0907</v>
@@ -2339,7 +2339,7 @@
         <v>0.7839</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="D42" t="n">
         <v>-0.1047</v>
@@ -2385,7 +2385,7 @@
         <v>0.7204</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
       <c r="D43" t="n">
         <v>-0.1303</v>
@@ -2431,7 +2431,7 @@
         <v>0.7053</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.386</v>
       </c>
       <c r="D44" t="n">
         <v>-0.1364</v>
@@ -2477,7 +2477,7 @@
         <v>0.6576</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.3599</v>
       </c>
       <c r="D45" t="n">
         <v>-0.1557</v>
@@ -2523,7 +2523,7 @@
         <v>0.5784</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>0.3166</v>
       </c>
       <c r="D46" t="n">
         <v>-0.1877</v>
@@ -2569,7 +2569,7 @@
         <v>0.5527</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>0.3025</v>
       </c>
       <c r="D47" t="n">
         <v>-0.1981</v>
@@ -2615,7 +2615,7 @@
         <v>0.4863</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.2662</v>
       </c>
       <c r="D48" t="n">
         <v>-0.2249</v>
@@ -2661,7 +2661,7 @@
         <v>0.4444</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>0.2432</v>
       </c>
       <c r="D49" t="n">
         <v>-0.2418</v>
@@ -2707,7 +2707,7 @@
         <v>0.3537</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>0.1936</v>
       </c>
       <c r="D50" t="n">
         <v>-0.2785</v>
@@ -2753,7 +2753,7 @@
         <v>0.2773</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>0.1518</v>
       </c>
       <c r="D51" t="n">
         <v>-0.3093</v>
@@ -2799,7 +2799,7 @@
         <v>0.2461</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>0.1347</v>
       </c>
       <c r="D52" t="n">
         <v>-0.3219</v>
@@ -2845,7 +2845,7 @@
         <v>0.0544</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>0.0298</v>
       </c>
       <c r="D53" t="n">
         <v>-0.3994</v>
@@ -2891,7 +2891,7 @@
         <v>0.0384</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="D54" t="n">
         <v>-0.4058</v>
@@ -2937,7 +2937,7 @@
         <v>0.0192</v>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>0.0105</v>
       </c>
       <c r="D55" t="n">
         <v>-0.4136</v>
@@ -2983,7 +2983,7 @@
         <v>-0.2062</v>
       </c>
       <c r="C56" t="n">
-        <v>-0</v>
+        <v>-0.1129</v>
       </c>
       <c r="D56" t="n">
         <v>-0.5047</v>
@@ -3029,7 +3029,7 @@
         <v>-0.3444</v>
       </c>
       <c r="C57" t="n">
-        <v>-0</v>
+        <v>-0.1885</v>
       </c>
       <c r="D57" t="n">
         <v>-0.5605</v>
@@ -3075,7 +3075,7 @@
         <v>-0.4153</v>
       </c>
       <c r="C58" t="n">
-        <v>-0</v>
+        <v>-0.2273</v>
       </c>
       <c r="D58" t="n">
         <v>-0.5891</v>
@@ -3121,7 +3121,7 @@
         <v>-0.4564</v>
       </c>
       <c r="C59" t="n">
-        <v>-0</v>
+        <v>-0.2498</v>
       </c>
       <c r="D59" t="n">
         <v>-0.6057</v>
@@ -3167,7 +3167,7 @@
         <v>-0.5945</v>
       </c>
       <c r="C60" t="n">
-        <v>-0</v>
+        <v>-0.3254</v>
       </c>
       <c r="D60" t="n">
         <v>-0.6615</v>
@@ -3213,7 +3213,7 @@
         <v>-0.6485</v>
       </c>
       <c r="C61" t="n">
-        <v>-0</v>
+        <v>-0.3549</v>
       </c>
       <c r="D61" t="n">
         <v>-0.6833</v>
@@ -3259,7 +3259,7 @@
         <v>-0.7175</v>
       </c>
       <c r="C62" t="n">
-        <v>-0</v>
+        <v>-0.3927</v>
       </c>
       <c r="D62" t="n">
         <v>-0.7112000000000001</v>
@@ -3305,7 +3305,7 @@
         <v>-0.8621</v>
       </c>
       <c r="C63" t="n">
-        <v>-0</v>
+        <v>-0.4718</v>
       </c>
       <c r="D63" t="n">
         <v>-0.7696</v>
@@ -3351,7 +3351,7 @@
         <v>-0.9048</v>
       </c>
       <c r="C64" t="n">
-        <v>-0</v>
+        <v>-0.4952</v>
       </c>
       <c r="D64" t="n">
         <v>-0.7869</v>
@@ -3397,7 +3397,7 @@
         <v>-1.0715</v>
       </c>
       <c r="C65" t="n">
-        <v>-0</v>
+        <v>-0.5864</v>
       </c>
       <c r="D65" t="n">
         <v>-0.8542</v>
@@ -3443,7 +3443,7 @@
         <v>-1.1079</v>
       </c>
       <c r="C66" t="n">
-        <v>-0</v>
+        <v>-0.6063</v>
       </c>
       <c r="D66" t="n">
         <v>-0.8689</v>
@@ -3489,7 +3489,7 @@
         <v>-1.2073</v>
       </c>
       <c r="C67" t="n">
-        <v>-0</v>
+        <v>-0.6608000000000001</v>
       </c>
       <c r="D67" t="n">
         <v>-0.9091</v>
@@ -3535,7 +3535,7 @@
         <v>-1.2135</v>
       </c>
       <c r="C68" t="n">
-        <v>-0</v>
+        <v>-0.6641</v>
       </c>
       <c r="D68" t="n">
         <v>-0.9116</v>
@@ -3581,7 +3581,7 @@
         <v>-1.3063</v>
       </c>
       <c r="C69" t="n">
-        <v>-0</v>
+        <v>-0.7149</v>
       </c>
       <c r="D69" t="n">
         <v>-0.9491000000000001</v>
@@ -3627,7 +3627,7 @@
         <v>-1.3315</v>
       </c>
       <c r="C70" t="n">
-        <v>-0</v>
+        <v>-0.7287</v>
       </c>
       <c r="D70" t="n">
         <v>-0.9593</v>
@@ -3673,7 +3673,7 @@
         <v>-1.4123</v>
       </c>
       <c r="C71" t="n">
-        <v>-0</v>
+        <v>-0.7729</v>
       </c>
       <c r="D71" t="n">
         <v>-0.9919</v>
@@ -3719,7 +3719,7 @@
         <v>-1.464</v>
       </c>
       <c r="C72" t="n">
-        <v>-0</v>
+        <v>-0.8012</v>
       </c>
       <c r="D72" t="n">
         <v>-1.0128</v>
@@ -3765,7 +3765,7 @@
         <v>-1.5209</v>
       </c>
       <c r="C73" t="n">
-        <v>-0</v>
+        <v>-0.8324</v>
       </c>
       <c r="D73" t="n">
         <v>-1.0358</v>
@@ -3811,7 +3811,7 @@
         <v>-1.5687</v>
       </c>
       <c r="C74" t="n">
-        <v>-0</v>
+        <v>-0.8585</v>
       </c>
       <c r="D74" t="n">
         <v>-1.0551</v>
@@ -3857,7 +3857,7 @@
         <v>-1.6806</v>
       </c>
       <c r="C75" t="n">
-        <v>-0</v>
+        <v>-0.9198</v>
       </c>
       <c r="D75" t="n">
         <v>-1.1003</v>
@@ -3903,7 +3903,7 @@
         <v>-1.9802</v>
       </c>
       <c r="C76" t="n">
-        <v>-0</v>
+        <v>-1.0838</v>
       </c>
       <c r="D76" t="n">
         <v>-1.2213</v>
@@ -3949,7 +3949,7 @@
         <v>-1.9874</v>
       </c>
       <c r="C77" t="n">
-        <v>-0</v>
+        <v>-1.0877</v>
       </c>
       <c r="D77" t="n">
         <v>-1.2242</v>
@@ -3995,7 +3995,7 @@
         <v>-2.1757</v>
       </c>
       <c r="C78" t="n">
-        <v>-0</v>
+        <v>-1.1908</v>
       </c>
       <c r="D78" t="n">
         <v>-1.3003</v>
@@ -4041,7 +4041,7 @@
         <v>-2.8373</v>
       </c>
       <c r="C79" t="n">
-        <v>-0</v>
+        <v>-1.5528</v>
       </c>
       <c r="D79" t="n">
         <v>-1.5676</v>
@@ -4087,7 +4087,7 @@
         <v>-2.9134</v>
       </c>
       <c r="C80" t="n">
-        <v>-0</v>
+        <v>-1.5945</v>
       </c>
       <c r="D80" t="n">
         <v>-1.5983</v>
@@ -4133,7 +4133,7 @@
         <v>-3.4208</v>
       </c>
       <c r="C81" t="n">
-        <v>-0</v>
+        <v>-1.8722</v>
       </c>
       <c r="D81" t="n">
         <v>-1.8033</v>

--- a/database/event/6865/event_6865_evp_summary.xlsx
+++ b/database/event/6865/event_6865_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.8843</v>
+        <v>7.8687</v>
       </c>
       <c r="C2" t="n">
-        <v>4.3151</v>
+        <v>4.3065</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7637</v>
+        <v>2.691</v>
       </c>
       <c r="E2" t="n">
-        <v>7.8843</v>
+        <v>7.8687</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3946</v>
+        <v>1.3791</v>
       </c>
       <c r="G2" t="n">
         <v>6.4896</v>
       </c>
       <c r="H2" t="n">
-        <v>1.3946</v>
+        <v>1.3791</v>
       </c>
       <c r="I2" t="n">
         <v>1.4142</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.6184</v>
+        <v>6.5851</v>
       </c>
       <c r="C3" t="n">
-        <v>3.6222</v>
+        <v>3.604</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2523</v>
+        <v>2.1796</v>
       </c>
       <c r="E3" t="n">
-        <v>6.6184</v>
+        <v>6.5851</v>
       </c>
       <c r="F3" t="n">
-        <v>2.986</v>
+        <v>2.9527</v>
       </c>
       <c r="G3" t="n">
         <v>3.6324</v>
       </c>
       <c r="H3" t="n">
-        <v>2.986</v>
+        <v>2.9527</v>
       </c>
       <c r="I3" t="n">
         <v>3.0279</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.4982</v>
+        <v>6.4672</v>
       </c>
       <c r="C4" t="n">
-        <v>3.5564</v>
+        <v>3.5395</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2038</v>
+        <v>2.1326</v>
       </c>
       <c r="E4" t="n">
-        <v>6.4982</v>
+        <v>6.4672</v>
       </c>
       <c r="F4" t="n">
-        <v>4.2416</v>
+        <v>4.2106</v>
       </c>
       <c r="G4" t="n">
         <v>2.2566</v>
       </c>
       <c r="H4" t="n">
-        <v>4.3477</v>
+        <v>4.2992</v>
       </c>
       <c r="I4" t="n">
         <v>4.4087</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.3745</v>
+        <v>6.3528</v>
       </c>
       <c r="C5" t="n">
-        <v>3.4887</v>
+        <v>3.4769</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1538</v>
+        <v>2.087</v>
       </c>
       <c r="E5" t="n">
-        <v>6.3745</v>
+        <v>6.3528</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9396</v>
+        <v>1.918</v>
       </c>
       <c r="G5" t="n">
         <v>4.4349</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9396</v>
+        <v>1.918</v>
       </c>
       <c r="I5" t="n">
         <v>1.9668</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.5022</v>
+        <v>5.5308</v>
       </c>
       <c r="C6" t="n">
-        <v>3.0113</v>
+        <v>3.027</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8014</v>
+        <v>1.7596</v>
       </c>
       <c r="E6" t="n">
-        <v>5.5022</v>
+        <v>5.5308</v>
       </c>
       <c r="F6" t="n">
-        <v>4.724</v>
+        <v>4.7526</v>
       </c>
       <c r="G6" t="n">
         <v>0.7782</v>
       </c>
       <c r="H6" t="n">
-        <v>6.4451</v>
+        <v>6.5604</v>
       </c>
       <c r="I6" t="n">
-        <v>5.2239</v>
+        <v>5.3174</v>
       </c>
       <c r="J6" t="n">
         <v>0.7782</v>
@@ -713,7 +713,7 @@
         <v>37</v>
       </c>
       <c r="M6" t="n">
-        <v>6.0021</v>
+        <v>6.0956</v>
       </c>
       <c r="N6" t="n">
         <v>144</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.4332</v>
+        <v>5.4137</v>
       </c>
       <c r="C7" t="n">
-        <v>2.9736</v>
+        <v>2.9629</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7735</v>
+        <v>1.7129</v>
       </c>
       <c r="E7" t="n">
-        <v>5.4332</v>
+        <v>5.4137</v>
       </c>
       <c r="F7" t="n">
-        <v>2.6202</v>
+        <v>2.6007</v>
       </c>
       <c r="G7" t="n">
         <v>2.813</v>
       </c>
       <c r="H7" t="n">
-        <v>2.6202</v>
+        <v>2.6007</v>
       </c>
       <c r="I7" t="n">
         <v>2.6447</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.7116</v>
+        <v>4.7133</v>
       </c>
       <c r="C8" t="n">
-        <v>2.5786</v>
+        <v>2.5796</v>
       </c>
       <c r="D8" t="n">
-        <v>1.482</v>
+        <v>1.4339</v>
       </c>
       <c r="E8" t="n">
-        <v>4.7116</v>
+        <v>4.7133</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2266</v>
+        <v>-0.2249</v>
       </c>
       <c r="G8" t="n">
         <v>4.9382</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2266</v>
+        <v>-0.2249</v>
       </c>
       <c r="I8" t="n">
         <v>-0.2287</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.3935</v>
+        <v>4.3702</v>
       </c>
       <c r="C9" t="n">
-        <v>2.4045</v>
+        <v>2.3918</v>
       </c>
       <c r="D9" t="n">
-        <v>1.3535</v>
+        <v>1.2972</v>
       </c>
       <c r="E9" t="n">
-        <v>4.3935</v>
+        <v>4.3702</v>
       </c>
       <c r="F9" t="n">
-        <v>3.1271</v>
+        <v>3.1038</v>
       </c>
       <c r="G9" t="n">
         <v>1.2664</v>
       </c>
       <c r="H9" t="n">
-        <v>3.1271</v>
+        <v>3.1038</v>
       </c>
       <c r="I9" t="n">
         <v>3.1562</v>
@@ -870,7 +870,7 @@
         <v>2.2552</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2433</v>
+        <v>1.1977</v>
       </c>
       <c r="E10" t="n">
         <v>4.1206</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.0563</v>
+        <v>4.0421</v>
       </c>
       <c r="C11" t="n">
-        <v>2.22</v>
+        <v>2.2122</v>
       </c>
       <c r="D11" t="n">
-        <v>1.2173</v>
+        <v>1.1665</v>
       </c>
       <c r="E11" t="n">
-        <v>4.0563</v>
+        <v>4.0421</v>
       </c>
       <c r="F11" t="n">
-        <v>4.0563</v>
+        <v>4.0421</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>4.0572</v>
+        <v>4.0421</v>
       </c>
       <c r="I11" t="n">
         <v>4.0761</v>
@@ -962,7 +962,7 @@
         <v>1.7495</v>
       </c>
       <c r="D12" t="n">
-        <v>0.87</v>
+        <v>0.8296</v>
       </c>
       <c r="E12" t="n">
         <v>3.1966</v>
@@ -998,185 +998,185 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>volt</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.1023</v>
+        <v>3.1883</v>
       </c>
       <c r="C13" t="n">
-        <v>1.6979</v>
+        <v>1.7449</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8319</v>
+        <v>0.8263</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1023</v>
+        <v>3.1883</v>
       </c>
       <c r="F13" t="n">
-        <v>3.1023</v>
+        <v>3.1883</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3.1023</v>
+        <v>3.1883</v>
       </c>
       <c r="I13" t="n">
-        <v>3.1023</v>
+        <v>3.2151</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>125</v>
+        <v>185</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1023</v>
+        <v>3.2151</v>
       </c>
       <c r="N13" t="n">
-        <v>125</v>
+        <v>185</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.0988</v>
+        <v>3.1023</v>
       </c>
       <c r="C14" t="n">
-        <v>1.696</v>
+        <v>1.6979</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8305</v>
+        <v>0.792</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0988</v>
+        <v>3.1023</v>
       </c>
       <c r="F14" t="n">
-        <v>2.9946</v>
+        <v>3.1023</v>
       </c>
       <c r="G14" t="n">
-        <v>0.1042</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.9946</v>
+        <v>3.1023</v>
       </c>
       <c r="I14" t="n">
-        <v>2.4272</v>
+        <v>3.1023</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1042</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>157</v>
+        <v>125</v>
       </c>
       <c r="L14" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.5314</v>
+        <v>3.1023</v>
       </c>
       <c r="N14" t="n">
-        <v>196</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>nafany</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.9851</v>
+        <v>3.0988</v>
       </c>
       <c r="C15" t="n">
-        <v>1.6337</v>
+        <v>1.696</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7846</v>
+        <v>0.7907</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9851</v>
+        <v>3.0988</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5105</v>
+        <v>2.9946</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4746</v>
+        <v>0.1042</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5105</v>
+        <v>2.9946</v>
       </c>
       <c r="I15" t="n">
-        <v>2.5221</v>
+        <v>2.4272</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4746</v>
+        <v>0.1042</v>
       </c>
       <c r="K15" t="n">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="L15" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9967</v>
+        <v>2.5314</v>
       </c>
       <c r="N15" t="n">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>volt</t>
+          <t>nafany</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.9575</v>
+        <v>2.9757</v>
       </c>
       <c r="C16" t="n">
-        <v>1.6186</v>
+        <v>1.6286</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7734</v>
+        <v>0.7416</v>
       </c>
       <c r="E16" t="n">
-        <v>2.9575</v>
+        <v>2.9757</v>
       </c>
       <c r="F16" t="n">
-        <v>2.9575</v>
+        <v>2.5011</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.4746</v>
       </c>
       <c r="H16" t="n">
-        <v>2.9575</v>
+        <v>2.5011</v>
       </c>
       <c r="I16" t="n">
-        <v>2.9713</v>
+        <v>2.5221</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>0.4746</v>
       </c>
       <c r="K16" t="n">
-        <v>185</v>
+        <v>150</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9713</v>
+        <v>2.9967</v>
       </c>
       <c r="N16" t="n">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="17">
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.544</v>
+        <v>2.8662</v>
       </c>
       <c r="C17" t="n">
-        <v>1.3923</v>
+        <v>1.5687</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6064000000000001</v>
+        <v>0.698</v>
       </c>
       <c r="E17" t="n">
-        <v>2.544</v>
+        <v>2.8662</v>
       </c>
       <c r="F17" t="n">
-        <v>2.9942</v>
+        <v>3.3164</v>
       </c>
       <c r="G17" t="n">
         <v>-0.4502</v>
       </c>
       <c r="H17" t="n">
-        <v>2.9942</v>
+        <v>3.3164</v>
       </c>
       <c r="I17" t="n">
-        <v>3.0082</v>
+        <v>3.3444</v>
       </c>
       <c r="J17" t="n">
         <v>-0.4502</v>
@@ -1219,7 +1219,7 @@
         <v>43</v>
       </c>
       <c r="M17" t="n">
-        <v>2.558</v>
+        <v>2.8942</v>
       </c>
       <c r="N17" t="n">
         <v>193</v>
@@ -1228,274 +1228,274 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>sdy</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.5021</v>
+        <v>2.8053</v>
       </c>
       <c r="C18" t="n">
-        <v>1.3694</v>
+        <v>1.5353</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5894</v>
+        <v>0.6737</v>
       </c>
       <c r="E18" t="n">
-        <v>2.5021</v>
+        <v>2.8053</v>
       </c>
       <c r="F18" t="n">
-        <v>2.5021</v>
+        <v>-0.0718</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>2.8771</v>
       </c>
       <c r="H18" t="n">
-        <v>2.5021</v>
+        <v>-0.0718</v>
       </c>
       <c r="I18" t="n">
-        <v>2.5137</v>
+        <v>-0.0731</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>2.8771</v>
       </c>
       <c r="K18" t="n">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="M18" t="n">
-        <v>2.5137</v>
+        <v>2.804</v>
       </c>
       <c r="N18" t="n">
-        <v>181</v>
+        <v>339</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DemQQ</t>
+          <t>jL</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.4401</v>
+        <v>2.5998</v>
       </c>
       <c r="C19" t="n">
-        <v>1.3355</v>
+        <v>1.4229</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5644</v>
+        <v>0.5919</v>
       </c>
       <c r="E19" t="n">
-        <v>2.4401</v>
+        <v>2.5998</v>
       </c>
       <c r="F19" t="n">
-        <v>2.4401</v>
+        <v>2.5998</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.4401</v>
+        <v>2.5998</v>
       </c>
       <c r="I19" t="n">
-        <v>2.4514</v>
+        <v>2.5998</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>181</v>
+        <v>144</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.4514</v>
+        <v>2.5998</v>
       </c>
       <c r="N19" t="n">
-        <v>181</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.4218</v>
+        <v>2.5057</v>
       </c>
       <c r="C20" t="n">
-        <v>1.3254</v>
+        <v>1.3714</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5544</v>
       </c>
       <c r="E20" t="n">
-        <v>2.4218</v>
+        <v>2.5057</v>
       </c>
       <c r="F20" t="n">
-        <v>2.4218</v>
+        <v>3.5057</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H20" t="n">
-        <v>2.4218</v>
+        <v>3.5057</v>
       </c>
       <c r="I20" t="n">
-        <v>2.4218</v>
+        <v>2.8415</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K20" t="n">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="M20" t="n">
-        <v>2.4218</v>
+        <v>1.8415</v>
       </c>
       <c r="N20" t="n">
-        <v>144</v>
+        <v>196</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>sdy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.2581</v>
+        <v>2.4927</v>
       </c>
       <c r="C21" t="n">
-        <v>1.2359</v>
+        <v>1.3642</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4909</v>
+        <v>0.5492</v>
       </c>
       <c r="E21" t="n">
-        <v>2.2581</v>
+        <v>2.4927</v>
       </c>
       <c r="F21" t="n">
-        <v>3.2581</v>
+        <v>2.4927</v>
       </c>
       <c r="G21" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>3.2581</v>
+        <v>2.4927</v>
       </c>
       <c r="I21" t="n">
-        <v>2.6408</v>
+        <v>2.5137</v>
       </c>
       <c r="J21" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="L21" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.6408</v>
+        <v>2.5137</v>
       </c>
       <c r="N21" t="n">
-        <v>196</v>
+        <v>181</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>DemQQ</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.103</v>
+        <v>2.431</v>
       </c>
       <c r="C22" t="n">
-        <v>1.151</v>
+        <v>1.3305</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4282</v>
+        <v>0.5246</v>
       </c>
       <c r="E22" t="n">
-        <v>2.103</v>
+        <v>2.431</v>
       </c>
       <c r="F22" t="n">
-        <v>3.103</v>
+        <v>2.431</v>
       </c>
       <c r="G22" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>3.103</v>
+        <v>2.431</v>
       </c>
       <c r="I22" t="n">
-        <v>2.5151</v>
+        <v>2.4514</v>
       </c>
       <c r="J22" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>107</v>
+        <v>181</v>
       </c>
       <c r="L22" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.5151</v>
+        <v>2.4514</v>
       </c>
       <c r="N22" t="n">
-        <v>144</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.0998</v>
+        <v>2.4218</v>
       </c>
       <c r="C23" t="n">
-        <v>1.1492</v>
+        <v>1.3254</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4269</v>
+        <v>0.5209</v>
       </c>
       <c r="E23" t="n">
-        <v>2.0998</v>
+        <v>2.4218</v>
       </c>
       <c r="F23" t="n">
-        <v>2.1364</v>
+        <v>2.4218</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.0366</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2.1364</v>
+        <v>2.4218</v>
       </c>
       <c r="I23" t="n">
-        <v>1.7316</v>
+        <v>2.4218</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.0366</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>107</v>
+        <v>144</v>
       </c>
       <c r="L23" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.695</v>
+        <v>2.4218</v>
       </c>
       <c r="N23" t="n">
         <v>144</v>
@@ -1504,277 +1504,277 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>br0</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.0838</v>
+        <v>2.103</v>
       </c>
       <c r="C24" t="n">
-        <v>1.1405</v>
+        <v>1.151</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4204</v>
+        <v>0.3939</v>
       </c>
       <c r="E24" t="n">
-        <v>2.0838</v>
+        <v>2.103</v>
       </c>
       <c r="F24" t="n">
-        <v>2.0838</v>
+        <v>3.103</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H24" t="n">
-        <v>2.0838</v>
+        <v>3.103</v>
       </c>
       <c r="I24" t="n">
-        <v>2.0935</v>
+        <v>2.5151</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K24" t="n">
-        <v>181</v>
+        <v>107</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M24" t="n">
-        <v>2.0935</v>
+        <v>1.5151</v>
       </c>
       <c r="N24" t="n">
-        <v>181</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1.886</v>
+        <v>2.0998</v>
       </c>
       <c r="C25" t="n">
-        <v>1.0322</v>
+        <v>1.1492</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3405</v>
+        <v>0.3927</v>
       </c>
       <c r="E25" t="n">
-        <v>1.886</v>
+        <v>2.0998</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.9911</v>
+        <v>2.1364</v>
       </c>
       <c r="G25" t="n">
-        <v>2.8771</v>
+        <v>-0.0366</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.9911</v>
+        <v>2.1364</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.0003</v>
+        <v>1.7316</v>
       </c>
       <c r="J25" t="n">
-        <v>2.8771</v>
+        <v>-0.0366</v>
       </c>
       <c r="K25" t="n">
-        <v>177</v>
+        <v>107</v>
       </c>
       <c r="L25" t="n">
-        <v>162</v>
+        <v>37</v>
       </c>
       <c r="M25" t="n">
-        <v>1.8768</v>
+        <v>1.695</v>
       </c>
       <c r="N25" t="n">
-        <v>339</v>
+        <v>144</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.7342</v>
+        <v>2.0889</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9491000000000001</v>
+        <v>1.1432</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2792</v>
+        <v>0.3883</v>
       </c>
       <c r="E26" t="n">
-        <v>1.7342</v>
+        <v>2.0889</v>
       </c>
       <c r="F26" t="n">
-        <v>1.7342</v>
+        <v>2.7216</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-0.6327</v>
       </c>
       <c r="H26" t="n">
-        <v>1.7342</v>
+        <v>2.7216</v>
       </c>
       <c r="I26" t="n">
-        <v>1.7342</v>
+        <v>2.2059</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>-0.6327</v>
       </c>
       <c r="K26" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="M26" t="n">
-        <v>1.7342</v>
+        <v>1.5732</v>
       </c>
       <c r="N26" t="n">
-        <v>151</v>
+        <v>196</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>acoR</t>
+          <t>br0</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.72</v>
+        <v>2.076</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9414</v>
+        <v>1.1362</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2735</v>
+        <v>0.3832</v>
       </c>
       <c r="E27" t="n">
-        <v>1.72</v>
+        <v>2.076</v>
       </c>
       <c r="F27" t="n">
-        <v>1.72</v>
+        <v>2.076</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.72</v>
+        <v>2.076</v>
       </c>
       <c r="I27" t="n">
-        <v>1.728</v>
+        <v>2.0935</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.728</v>
+        <v>2.0935</v>
       </c>
       <c r="N27" t="n">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>jL</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.6691</v>
+        <v>1.9254</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9135</v>
+        <v>1.0538</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2529</v>
+        <v>0.3232</v>
       </c>
       <c r="E28" t="n">
-        <v>1.6691</v>
+        <v>1.9254</v>
       </c>
       <c r="F28" t="n">
-        <v>1.6691</v>
+        <v>1.9254</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.6691</v>
+        <v>1.9254</v>
       </c>
       <c r="I28" t="n">
-        <v>1.6691</v>
+        <v>1.9254</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.6691</v>
+        <v>1.9254</v>
       </c>
       <c r="N28" t="n">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>acoR</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.5237</v>
+        <v>1.7135</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8339</v>
+        <v>0.9378</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1942</v>
+        <v>0.2387</v>
       </c>
       <c r="E29" t="n">
-        <v>1.5237</v>
+        <v>1.7135</v>
       </c>
       <c r="F29" t="n">
-        <v>2.1564</v>
+        <v>1.7135</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.6327</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2.1564</v>
+        <v>1.7135</v>
       </c>
       <c r="I29" t="n">
-        <v>1.7478</v>
+        <v>1.728</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.6327</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>157</v>
+        <v>185</v>
       </c>
       <c r="L29" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.1151</v>
+        <v>1.728</v>
       </c>
       <c r="N29" t="n">
-        <v>196</v>
+        <v>185</v>
       </c>
     </row>
     <row r="30">
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.4499</v>
+        <v>1.5573</v>
       </c>
       <c r="C30" t="n">
-        <v>0.7935</v>
+        <v>0.8522999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1644</v>
+        <v>0.1765</v>
       </c>
       <c r="E30" t="n">
-        <v>1.4499</v>
+        <v>1.5573</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8934</v>
+        <v>1.0008</v>
       </c>
       <c r="G30" t="n">
         <v>0.5565</v>
       </c>
       <c r="H30" t="n">
-        <v>0.8934</v>
+        <v>1.0008</v>
       </c>
       <c r="I30" t="n">
-        <v>0.9016999999999999</v>
+        <v>1.0177</v>
       </c>
       <c r="J30" t="n">
         <v>0.5565</v>
@@ -1817,7 +1817,7 @@
         <v>162</v>
       </c>
       <c r="M30" t="n">
-        <v>1.4582</v>
+        <v>1.5742</v>
       </c>
       <c r="N30" t="n">
         <v>339</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.3905</v>
+        <v>1.4293</v>
       </c>
       <c r="C31" t="n">
-        <v>0.761</v>
+        <v>0.7823</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1404</v>
+        <v>0.1255</v>
       </c>
       <c r="E31" t="n">
-        <v>1.3905</v>
+        <v>1.4293</v>
       </c>
       <c r="F31" t="n">
-        <v>1.3905</v>
+        <v>1.4293</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.3905</v>
+        <v>1.4293</v>
       </c>
       <c r="I31" t="n">
-        <v>1.3905</v>
+        <v>1.4293</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.3905</v>
+        <v>1.4293</v>
       </c>
       <c r="N31" t="n">
         <v>151</v>
@@ -1872,415 +1872,415 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>Nexius</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.2126</v>
+        <v>1.2825</v>
       </c>
       <c r="C32" t="n">
-        <v>0.6637</v>
+        <v>0.7019</v>
       </c>
       <c r="D32" t="n">
-        <v>0.06850000000000001</v>
+        <v>0.067</v>
       </c>
       <c r="E32" t="n">
-        <v>1.2126</v>
+        <v>1.2825</v>
       </c>
       <c r="F32" t="n">
-        <v>1.2126</v>
+        <v>1.9692</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-0.6867</v>
       </c>
       <c r="H32" t="n">
-        <v>1.2126</v>
+        <v>1.9692</v>
       </c>
       <c r="I32" t="n">
-        <v>1.2126</v>
+        <v>1.5961</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-0.6867</v>
       </c>
       <c r="K32" t="n">
-        <v>125</v>
+        <v>157</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="M32" t="n">
-        <v>1.2126</v>
+        <v>0.9094000000000001</v>
       </c>
       <c r="N32" t="n">
-        <v>125</v>
+        <v>196</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>malta</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.1817</v>
+        <v>1.2556</v>
       </c>
       <c r="C33" t="n">
-        <v>0.6467000000000001</v>
+        <v>0.6872</v>
       </c>
       <c r="D33" t="n">
-        <v>0.056</v>
+        <v>0.0563</v>
       </c>
       <c r="E33" t="n">
-        <v>1.1817</v>
+        <v>1.2556</v>
       </c>
       <c r="F33" t="n">
-        <v>1.1817</v>
+        <v>1.2556</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.1817</v>
+        <v>1.2556</v>
       </c>
       <c r="I33" t="n">
-        <v>1.1817</v>
+        <v>1.2556</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>57</v>
+        <v>144</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.1817</v>
+        <v>1.2556</v>
       </c>
       <c r="N33" t="n">
-        <v>57</v>
+        <v>144</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.1572</v>
+        <v>1.2126</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6333</v>
+        <v>0.6637</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0461</v>
+        <v>0.0392</v>
       </c>
       <c r="E34" t="n">
-        <v>1.1572</v>
+        <v>1.2126</v>
       </c>
       <c r="F34" t="n">
-        <v>1.5724</v>
+        <v>1.2126</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.4152</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.5724</v>
+        <v>1.2126</v>
       </c>
       <c r="I34" t="n">
-        <v>1.5724</v>
+        <v>1.2126</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.4152</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="L34" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.1572</v>
+        <v>1.2126</v>
       </c>
       <c r="N34" t="n">
-        <v>162</v>
+        <v>125</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.0656</v>
+        <v>1.204</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.6589</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0091</v>
+        <v>0.0358</v>
       </c>
       <c r="E35" t="n">
-        <v>1.0656</v>
+        <v>1.204</v>
       </c>
       <c r="F35" t="n">
-        <v>1.0656</v>
+        <v>1.6192</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>-0.4152</v>
       </c>
       <c r="H35" t="n">
-        <v>1.0656</v>
+        <v>1.6192</v>
       </c>
       <c r="I35" t="n">
-        <v>1.0656</v>
+        <v>1.6192</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>-0.4152</v>
       </c>
       <c r="K35" t="n">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="M35" t="n">
-        <v>1.0656</v>
+        <v>1.204</v>
       </c>
       <c r="N35" t="n">
-        <v>144</v>
+        <v>162</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>malta</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.0088</v>
+        <v>1.1817</v>
       </c>
       <c r="C36" t="n">
-        <v>0.5521</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0138</v>
+        <v>0.0269</v>
       </c>
       <c r="E36" t="n">
-        <v>1.0088</v>
+        <v>1.1817</v>
       </c>
       <c r="F36" t="n">
-        <v>1.0088</v>
+        <v>1.1817</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.0088</v>
+        <v>1.1817</v>
       </c>
       <c r="I36" t="n">
-        <v>1.0088</v>
+        <v>1.1817</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1.0088</v>
+        <v>1.1817</v>
       </c>
       <c r="N36" t="n">
-        <v>109</v>
+        <v>57</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>INS</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.9857</v>
+        <v>1.1007</v>
       </c>
       <c r="C37" t="n">
-        <v>0.5395</v>
+        <v>0.6024</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.0232</v>
+        <v>-0.0054</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9857</v>
+        <v>1.1007</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9857</v>
+        <v>1.1007</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.9857</v>
+        <v>1.1007</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9903</v>
+        <v>1.1007</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>185</v>
+        <v>66</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.9903</v>
+        <v>1.1007</v>
       </c>
       <c r="N37" t="n">
-        <v>185</v>
+        <v>66</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>INS</t>
+          <t>afro</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.9719</v>
+        <v>1.0826</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5319</v>
+        <v>0.5925</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.0287</v>
+        <v>-0.0126</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9719</v>
+        <v>1.0826</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9719</v>
+        <v>1.0826</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.9719</v>
+        <v>1.0826</v>
       </c>
       <c r="I38" t="n">
-        <v>0.9719</v>
+        <v>1.0826</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>66</v>
+        <v>151</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>0.9719</v>
+        <v>1.0826</v>
       </c>
       <c r="N38" t="n">
-        <v>66</v>
+        <v>151</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Nexius</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.9423</v>
+        <v>1.0088</v>
       </c>
       <c r="C39" t="n">
-        <v>0.5157</v>
+        <v>0.5521</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.0407</v>
+        <v>-0.042</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9423</v>
+        <v>1.0088</v>
       </c>
       <c r="F39" t="n">
-        <v>1.629</v>
+        <v>1.0088</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.6867</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1.629</v>
+        <v>1.0088</v>
       </c>
       <c r="I39" t="n">
-        <v>1.3204</v>
+        <v>1.0088</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.6867</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>157</v>
+        <v>109</v>
       </c>
       <c r="L39" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.6337</v>
+        <v>1.0088</v>
       </c>
       <c r="N39" t="n">
-        <v>196</v>
+        <v>109</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>afro</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8275</v>
+        <v>0.982</v>
       </c>
       <c r="C40" t="n">
-        <v>0.4529</v>
+        <v>0.5374</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.0871</v>
+        <v>-0.0527</v>
       </c>
       <c r="E40" t="n">
-        <v>0.8275</v>
+        <v>0.982</v>
       </c>
       <c r="F40" t="n">
-        <v>0.8275</v>
+        <v>0.982</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.8275</v>
+        <v>0.982</v>
       </c>
       <c r="I40" t="n">
-        <v>0.8275</v>
+        <v>0.9903</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>151</v>
+        <v>185</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.8275</v>
+        <v>0.9903</v>
       </c>
       <c r="N40" t="n">
-        <v>151</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41">
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8186</v>
+        <v>0.8367</v>
       </c>
       <c r="C41" t="n">
-        <v>0.448</v>
+        <v>0.4579</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.0907</v>
+        <v>-0.1106</v>
       </c>
       <c r="E41" t="n">
-        <v>0.8186</v>
+        <v>0.8367</v>
       </c>
       <c r="F41" t="n">
-        <v>0.8186</v>
+        <v>0.8367</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.8186</v>
+        <v>0.8367</v>
       </c>
       <c r="I41" t="n">
-        <v>0.8186</v>
+        <v>0.8367</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.8186</v>
+        <v>0.8367</v>
       </c>
       <c r="N41" t="n">
         <v>105</v>
@@ -2342,7 +2342,7 @@
         <v>0.429</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.1047</v>
+        <v>-0.1316</v>
       </c>
       <c r="E42" t="n">
         <v>0.7839</v>
@@ -2388,7 +2388,7 @@
         <v>0.3943</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.1303</v>
+        <v>-0.1569</v>
       </c>
       <c r="E43" t="n">
         <v>0.7204</v>
@@ -2434,7 +2434,7 @@
         <v>0.386</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.1364</v>
+        <v>-0.1629</v>
       </c>
       <c r="E44" t="n">
         <v>0.7053</v>
@@ -2480,7 +2480,7 @@
         <v>0.3599</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.1557</v>
+        <v>-0.1819</v>
       </c>
       <c r="E45" t="n">
         <v>0.6576</v>
@@ -2520,28 +2520,28 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5784</v>
+        <v>0.6341</v>
       </c>
       <c r="C46" t="n">
-        <v>0.3166</v>
+        <v>0.347</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.1877</v>
+        <v>-0.1913</v>
       </c>
       <c r="E46" t="n">
-        <v>0.5784</v>
+        <v>0.6341</v>
       </c>
       <c r="F46" t="n">
-        <v>0.5784</v>
+        <v>0.6341</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.5784</v>
+        <v>0.6341</v>
       </c>
       <c r="I46" t="n">
-        <v>0.5784</v>
+        <v>0.6341</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.5784</v>
+        <v>0.6341</v>
       </c>
       <c r="N46" t="n">
         <v>125</v>
@@ -2572,7 +2572,7 @@
         <v>0.3025</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.1981</v>
+        <v>-0.2237</v>
       </c>
       <c r="E47" t="n">
         <v>0.5527</v>
@@ -2618,7 +2618,7 @@
         <v>0.2662</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.2249</v>
+        <v>-0.2502</v>
       </c>
       <c r="E48" t="n">
         <v>0.4863</v>
@@ -2658,28 +2658,28 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4444</v>
+        <v>0.4467</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2432</v>
+        <v>0.2445</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.2418</v>
+        <v>-0.2659</v>
       </c>
       <c r="E49" t="n">
-        <v>0.4444</v>
+        <v>0.4467</v>
       </c>
       <c r="F49" t="n">
-        <v>0.4444</v>
+        <v>0.4467</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.4444</v>
+        <v>0.4467</v>
       </c>
       <c r="I49" t="n">
-        <v>0.4444</v>
+        <v>0.4467</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -2691,7 +2691,7 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.4444</v>
+        <v>0.4467</v>
       </c>
       <c r="N49" t="n">
         <v>64</v>
@@ -2704,25 +2704,25 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.3537</v>
+        <v>0.3528</v>
       </c>
       <c r="C50" t="n">
-        <v>0.1936</v>
+        <v>0.1931</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.2785</v>
+        <v>-0.3034</v>
       </c>
       <c r="E50" t="n">
-        <v>0.3537</v>
+        <v>0.3528</v>
       </c>
       <c r="F50" t="n">
-        <v>0.2526</v>
+        <v>0.2517</v>
       </c>
       <c r="G50" t="n">
         <v>0.1011</v>
       </c>
       <c r="H50" t="n">
-        <v>0.2526</v>
+        <v>0.2517</v>
       </c>
       <c r="I50" t="n">
         <v>0.2538</v>
@@ -2756,7 +2756,7 @@
         <v>0.1518</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.3093</v>
+        <v>-0.3334</v>
       </c>
       <c r="E51" t="n">
         <v>0.2773</v>
@@ -2802,7 +2802,7 @@
         <v>0.1347</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.3219</v>
+        <v>-0.3459</v>
       </c>
       <c r="E52" t="n">
         <v>0.2461</v>
@@ -2838,323 +2838,323 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Westmelon</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.0544</v>
+        <v>0.0862</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0298</v>
+        <v>0.0472</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.3994</v>
+        <v>-0.4096</v>
       </c>
       <c r="E53" t="n">
-        <v>0.0544</v>
+        <v>0.0862</v>
       </c>
       <c r="F53" t="n">
-        <v>0.0544</v>
+        <v>0.8725000000000001</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>-0.7863</v>
       </c>
       <c r="H53" t="n">
-        <v>0.0544</v>
+        <v>0.8725000000000001</v>
       </c>
       <c r="I53" t="n">
-        <v>0.0544</v>
+        <v>0.8725000000000001</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>-0.7863</v>
       </c>
       <c r="K53" t="n">
-        <v>64</v>
+        <v>131</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="M53" t="n">
-        <v>0.0544</v>
+        <v>0.08620000000000005</v>
       </c>
       <c r="N53" t="n">
-        <v>64</v>
+        <v>162</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>Westmelon</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.0384</v>
+        <v>0.0544</v>
       </c>
       <c r="C54" t="n">
-        <v>0.021</v>
+        <v>0.0298</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4058</v>
+        <v>-0.4222</v>
       </c>
       <c r="E54" t="n">
-        <v>0.0384</v>
+        <v>0.0544</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0384</v>
+        <v>0.0544</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.0384</v>
+        <v>0.0544</v>
       </c>
       <c r="I54" t="n">
-        <v>0.0384</v>
+        <v>0.0544</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>105</v>
+        <v>64</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.0384</v>
+        <v>0.0544</v>
       </c>
       <c r="N54" t="n">
-        <v>105</v>
+        <v>64</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Liazz</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.0192</v>
+        <v>0.0384</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0105</v>
+        <v>0.021</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.4136</v>
+        <v>-0.4286</v>
       </c>
       <c r="E55" t="n">
-        <v>0.0192</v>
+        <v>0.0384</v>
       </c>
       <c r="F55" t="n">
-        <v>0.0192</v>
+        <v>0.0384</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.0192</v>
+        <v>0.0384</v>
       </c>
       <c r="I55" t="n">
-        <v>0.0192</v>
+        <v>0.0384</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.0192</v>
+        <v>0.0384</v>
       </c>
       <c r="N55" t="n">
-        <v>66</v>
+        <v>105</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>nawwk</t>
+          <t>Liazz</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.2062</v>
+        <v>0.0192</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.1129</v>
+        <v>0.0105</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5047</v>
+        <v>-0.4363</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.2062</v>
+        <v>0.0192</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.2062</v>
+        <v>0.0192</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.2062</v>
+        <v>0.0192</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2062</v>
+        <v>0.0192</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>109</v>
+        <v>66</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.2062</v>
+        <v>0.0192</v>
       </c>
       <c r="N56" t="n">
-        <v>109</v>
+        <v>66</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>nawwk</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.3444</v>
+        <v>-0.2062</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.1885</v>
+        <v>-0.1129</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5605</v>
+        <v>-0.5261</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.3444</v>
+        <v>-0.2062</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.3444</v>
+        <v>-0.2062</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.3444</v>
+        <v>-0.2062</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.3444</v>
+        <v>-0.2062</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.3444</v>
+        <v>-0.2062</v>
       </c>
       <c r="N57" t="n">
-        <v>125</v>
+        <v>109</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>EmiliaQAQ</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.4153</v>
+        <v>-0.3444</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.2273</v>
+        <v>-0.1885</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5891</v>
+        <v>-0.5810999999999999</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.4153</v>
+        <v>-0.3444</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.4153</v>
+        <v>-0.3444</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.4153</v>
+        <v>-0.3444</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.4153</v>
+        <v>-0.3444</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>64</v>
+        <v>125</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.4153</v>
+        <v>-0.3444</v>
       </c>
       <c r="N58" t="n">
-        <v>64</v>
+        <v>125</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>EmiliaQAQ</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.4564</v>
+        <v>-0.4153</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.2498</v>
+        <v>-0.2273</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6057</v>
+        <v>-0.6094000000000001</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.4564</v>
+        <v>-0.4153</v>
       </c>
       <c r="F59" t="n">
-        <v>0.3299</v>
+        <v>-0.4153</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.7863</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>0.3299</v>
+        <v>-0.4153</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3299</v>
+        <v>-0.4153</v>
       </c>
       <c r="J59" t="n">
-        <v>-0.7863</v>
+        <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>131</v>
+        <v>64</v>
       </c>
       <c r="L59" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.4564</v>
+        <v>-0.4153</v>
       </c>
       <c r="N59" t="n">
-        <v>162</v>
+        <v>64</v>
       </c>
     </row>
     <row r="60">
@@ -3170,7 +3170,7 @@
         <v>-0.3254</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6615</v>
+        <v>-0.6808</v>
       </c>
       <c r="E60" t="n">
         <v>-0.5945</v>
@@ -3210,25 +3210,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.6485</v>
+        <v>-0.6463</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.3549</v>
+        <v>-0.3537</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6833</v>
+        <v>-0.7014</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.6485</v>
+        <v>-0.6463</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.5694</v>
+        <v>-0.5672</v>
       </c>
       <c r="G61" t="n">
         <v>-0.0791</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.5694</v>
+        <v>-0.5672</v>
       </c>
       <c r="I61" t="n">
         <v>-0.572</v>
@@ -3262,7 +3262,7 @@
         <v>-0.3927</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7112000000000001</v>
+        <v>-0.7298</v>
       </c>
       <c r="E62" t="n">
         <v>-0.7175</v>
@@ -3302,25 +3302,25 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.8621</v>
+        <v>-0.8589</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.4718</v>
+        <v>-0.4701</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7696</v>
+        <v>-0.7861</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.8621</v>
+        <v>-0.8589</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.8621</v>
+        <v>-0.8589</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.8621</v>
+        <v>-0.8589</v>
       </c>
       <c r="I63" t="n">
         <v>-0.8661</v>
@@ -3354,7 +3354,7 @@
         <v>-0.4952</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7869</v>
+        <v>-0.8044</v>
       </c>
       <c r="E64" t="n">
         <v>-0.9048</v>
@@ -3400,7 +3400,7 @@
         <v>-0.5864</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8542</v>
+        <v>-0.8708</v>
       </c>
       <c r="E65" t="n">
         <v>-1.0715</v>
@@ -3440,25 +3440,25 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-1.1079</v>
+        <v>-1.1038</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.6063</v>
+        <v>-0.6041</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8689</v>
+        <v>-0.8837</v>
       </c>
       <c r="E66" t="n">
-        <v>-1.1079</v>
+        <v>-1.1038</v>
       </c>
       <c r="F66" t="n">
-        <v>-1.1079</v>
+        <v>-1.1038</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-1.1079</v>
+        <v>-1.1038</v>
       </c>
       <c r="I66" t="n">
         <v>-1.1131</v>
@@ -3486,25 +3486,25 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-1.2073</v>
+        <v>-1.2028</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.6608000000000001</v>
+        <v>-0.6583</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.9091</v>
+        <v>-0.9231</v>
       </c>
       <c r="E67" t="n">
-        <v>-1.2073</v>
+        <v>-1.2028</v>
       </c>
       <c r="F67" t="n">
-        <v>-1.2073</v>
+        <v>-1.2028</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-1.2073</v>
+        <v>-1.2028</v>
       </c>
       <c r="I67" t="n">
         <v>-1.2129</v>
@@ -3532,25 +3532,25 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-1.2135</v>
+        <v>-1.2121</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.6641</v>
+        <v>-0.6634</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9116</v>
+        <v>-0.9268</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.2135</v>
+        <v>-1.2121</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.3768</v>
+        <v>-0.3754</v>
       </c>
       <c r="G68" t="n">
         <v>-0.8367</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.3768</v>
+        <v>-0.3754</v>
       </c>
       <c r="I68" t="n">
         <v>-0.3786</v>
@@ -3584,7 +3584,7 @@
         <v>-0.7149</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9491000000000001</v>
+        <v>-0.9643</v>
       </c>
       <c r="E69" t="n">
         <v>-1.3063</v>
@@ -3630,7 +3630,7 @@
         <v>-0.7287</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9593</v>
+        <v>-0.9744</v>
       </c>
       <c r="E70" t="n">
         <v>-1.3315</v>
@@ -3676,7 +3676,7 @@
         <v>-0.7729</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9919</v>
+        <v>-1.0066</v>
       </c>
       <c r="E71" t="n">
         <v>-1.4123</v>
@@ -3722,7 +3722,7 @@
         <v>-0.8012</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0128</v>
+        <v>-1.0272</v>
       </c>
       <c r="E72" t="n">
         <v>-1.464</v>
@@ -3768,7 +3768,7 @@
         <v>-0.8324</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0358</v>
+        <v>-1.0498</v>
       </c>
       <c r="E73" t="n">
         <v>-1.5209</v>
@@ -3814,7 +3814,7 @@
         <v>-0.8585</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0551</v>
+        <v>-1.0689</v>
       </c>
       <c r="E74" t="n">
         <v>-1.5687</v>
@@ -3860,7 +3860,7 @@
         <v>-0.9198</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.1003</v>
+        <v>-1.1135</v>
       </c>
       <c r="E75" t="n">
         <v>-1.6806</v>
@@ -3906,7 +3906,7 @@
         <v>-1.0838</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.2213</v>
+        <v>-1.2328</v>
       </c>
       <c r="E76" t="n">
         <v>-1.9802</v>
@@ -3952,7 +3952,7 @@
         <v>-1.0877</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.2242</v>
+        <v>-1.2357</v>
       </c>
       <c r="E77" t="n">
         <v>-1.9874</v>
@@ -3992,25 +3992,25 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-2.1757</v>
+        <v>-2.1443</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.1908</v>
+        <v>-1.1736</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.3003</v>
+        <v>-1.2982</v>
       </c>
       <c r="E78" t="n">
-        <v>-2.1757</v>
+        <v>-2.1443</v>
       </c>
       <c r="F78" t="n">
-        <v>-2.82</v>
+        <v>-2.7886</v>
       </c>
       <c r="G78" t="n">
         <v>0.6443</v>
       </c>
       <c r="H78" t="n">
-        <v>-2.82</v>
+        <v>-2.7886</v>
       </c>
       <c r="I78" t="n">
         <v>-2.8596</v>
@@ -4044,7 +4044,7 @@
         <v>-1.5528</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.5676</v>
+        <v>-1.5743</v>
       </c>
       <c r="E79" t="n">
         <v>-2.8373</v>
@@ -4090,7 +4090,7 @@
         <v>-1.5945</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.5983</v>
+        <v>-1.6046</v>
       </c>
       <c r="E80" t="n">
         <v>-2.9134</v>
@@ -4136,7 +4136,7 @@
         <v>-1.8722</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.8033</v>
+        <v>-1.8068</v>
       </c>
       <c r="E81" t="n">
         <v>-3.4208</v>

--- a/database/event/6865/event_6865_evp_summary.xlsx
+++ b/database/event/6865/event_6865_evp_summary.xlsx
@@ -496,16 +496,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.6226</v>
+        <v>7.8069</v>
       </c>
       <c r="C2" t="n">
-        <v>4.1718</v>
+        <v>4.2727</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8458</v>
+        <v>2.8734</v>
       </c>
       <c r="E2" t="n">
-        <v>7.6226</v>
+        <v>7.8069</v>
       </c>
       <c r="F2" t="n">
         <v>1.6593</v>
@@ -542,16 +542,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.3596</v>
+        <v>6.5214</v>
       </c>
       <c r="C3" t="n">
-        <v>3.4806</v>
+        <v>3.5691</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2708</v>
+        <v>2.2991</v>
       </c>
       <c r="E3" t="n">
-        <v>6.3596</v>
+        <v>6.5214</v>
       </c>
       <c r="F3" t="n">
         <v>3.1002</v>
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.1421</v>
+        <v>6.1112</v>
       </c>
       <c r="C4" t="n">
-        <v>3.3616</v>
+        <v>3.3446</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1718</v>
+        <v>2.1159</v>
       </c>
       <c r="E4" t="n">
-        <v>6.1421</v>
+        <v>6.1112</v>
       </c>
       <c r="F4" t="n">
         <v>2.1339</v>
@@ -634,16 +634,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.9523</v>
+        <v>6.0632</v>
       </c>
       <c r="C5" t="n">
-        <v>3.2577</v>
+        <v>3.3184</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0854</v>
+        <v>2.0945</v>
       </c>
       <c r="E5" t="n">
-        <v>5.9523</v>
+        <v>6.0632</v>
       </c>
       <c r="F5" t="n">
         <v>3.4439</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.7492</v>
+        <v>5.8284</v>
       </c>
       <c r="C6" t="n">
-        <v>3.1465</v>
+        <v>3.1899</v>
       </c>
       <c r="D6" t="n">
-        <v>1.993</v>
+        <v>1.9896</v>
       </c>
       <c r="E6" t="n">
-        <v>5.7492</v>
+        <v>5.8284</v>
       </c>
       <c r="F6" t="n">
-        <v>2.849</v>
+        <v>2.8489</v>
       </c>
       <c r="G6" t="n">
         <v>2.9002</v>
       </c>
       <c r="H6" t="n">
-        <v>3.5105</v>
+        <v>3.5104</v>
       </c>
       <c r="I6" t="n">
-        <v>3.6938</v>
+        <v>3.6936</v>
       </c>
       <c r="J6" t="n">
         <v>2.9002</v>
@@ -713,7 +713,7 @@
         <v>162</v>
       </c>
       <c r="M6" t="n">
-        <v>6.593999999999999</v>
+        <v>6.5938</v>
       </c>
       <c r="N6" t="n">
         <v>339</v>
@@ -726,16 +726,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.3494</v>
+        <v>5.6429</v>
       </c>
       <c r="C7" t="n">
-        <v>2.9277</v>
+        <v>3.0883</v>
       </c>
       <c r="D7" t="n">
-        <v>1.811</v>
+        <v>1.9067</v>
       </c>
       <c r="E7" t="n">
-        <v>5.3494</v>
+        <v>5.6429</v>
       </c>
       <c r="F7" t="n">
         <v>4.5807</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.2322</v>
+        <v>5.2885</v>
       </c>
       <c r="C8" t="n">
-        <v>2.8636</v>
+        <v>2.8944</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7576</v>
+        <v>1.7484</v>
       </c>
       <c r="E8" t="n">
-        <v>5.2322</v>
+        <v>5.2885</v>
       </c>
       <c r="F8" t="n">
-        <v>0.753</v>
+        <v>0.7524</v>
       </c>
       <c r="G8" t="n">
         <v>4.4792</v>
       </c>
       <c r="H8" t="n">
-        <v>0.753</v>
+        <v>0.7524</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7923</v>
+        <v>0.7917</v>
       </c>
       <c r="J8" t="n">
         <v>4.4792</v>
@@ -805,7 +805,7 @@
         <v>162</v>
       </c>
       <c r="M8" t="n">
-        <v>5.2715</v>
+        <v>5.270899999999999</v>
       </c>
       <c r="N8" t="n">
         <v>339</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.6175</v>
+        <v>4.6481</v>
       </c>
       <c r="C9" t="n">
-        <v>2.5271</v>
+        <v>2.5439</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4778</v>
+        <v>1.4624</v>
       </c>
       <c r="E9" t="n">
-        <v>4.6175</v>
+        <v>4.6481</v>
       </c>
       <c r="F9" t="n">
-        <v>3.0146</v>
+        <v>3.0221</v>
       </c>
       <c r="G9" t="n">
         <v>1.6029</v>
       </c>
       <c r="H9" t="n">
-        <v>3.873</v>
+        <v>3.8896</v>
       </c>
       <c r="I9" t="n">
-        <v>4.0752</v>
+        <v>4.0926</v>
       </c>
       <c r="J9" t="n">
         <v>1.6029</v>
@@ -851,7 +851,7 @@
         <v>162</v>
       </c>
       <c r="M9" t="n">
-        <v>5.6781</v>
+        <v>5.6955</v>
       </c>
       <c r="N9" t="n">
         <v>339</v>
@@ -864,16 +864,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.6751</v>
+        <v>3.8898</v>
       </c>
       <c r="C10" t="n">
-        <v>2.0114</v>
+        <v>2.1289</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0488</v>
+        <v>1.1237</v>
       </c>
       <c r="E10" t="n">
-        <v>3.6751</v>
+        <v>3.8898</v>
       </c>
       <c r="F10" t="n">
         <v>3.4452</v>
@@ -910,16 +910,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.441</v>
+        <v>3.5284</v>
       </c>
       <c r="C11" t="n">
-        <v>1.8832</v>
+        <v>1.9311</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9422</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>3.441</v>
+        <v>3.5284</v>
       </c>
       <c r="F11" t="n">
         <v>3.441</v>
@@ -952,139 +952,139 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>electroNic</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.2081</v>
+        <v>3.5197</v>
       </c>
       <c r="C12" t="n">
-        <v>1.7558</v>
+        <v>1.9263</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8362000000000001</v>
+        <v>0.9584</v>
       </c>
       <c r="E12" t="n">
-        <v>3.2081</v>
+        <v>3.5197</v>
       </c>
       <c r="F12" t="n">
-        <v>2.9602</v>
+        <v>3.1703</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2479</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>4.8725</v>
+        <v>4.2138</v>
       </c>
       <c r="I12" t="n">
-        <v>2.6311</v>
+        <v>4.2138</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2479</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>157</v>
+        <v>125</v>
       </c>
       <c r="L12" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.879</v>
+        <v>4.2138</v>
       </c>
       <c r="N12" t="n">
-        <v>196</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>JT</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.181</v>
+        <v>3.2258</v>
       </c>
       <c r="C13" t="n">
-        <v>1.741</v>
+        <v>1.7655</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8239</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>3.181</v>
+        <v>3.2258</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5424</v>
+        <v>2.9602</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6386</v>
+        <v>0.2479</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5424</v>
+        <v>4.8725</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5707</v>
+        <v>2.6311</v>
       </c>
       <c r="J13" t="n">
-        <v>2.6386</v>
+        <v>0.2479</v>
       </c>
       <c r="K13" t="n">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="L13" t="n">
-        <v>162</v>
+        <v>39</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2093</v>
+        <v>2.879</v>
       </c>
       <c r="N13" t="n">
-        <v>339</v>
+        <v>196</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>electroNic</t>
+          <t>JT</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.1703</v>
+        <v>3.1953</v>
       </c>
       <c r="C14" t="n">
-        <v>1.7351</v>
+        <v>1.7488</v>
       </c>
       <c r="D14" t="n">
-        <v>0.819</v>
+        <v>0.8135</v>
       </c>
       <c r="E14" t="n">
-        <v>3.1703</v>
+        <v>3.1953</v>
       </c>
       <c r="F14" t="n">
-        <v>3.1703</v>
+        <v>0.5421</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>2.6386</v>
       </c>
       <c r="H14" t="n">
-        <v>4.2138</v>
+        <v>0.5421</v>
       </c>
       <c r="I14" t="n">
-        <v>4.2138</v>
+        <v>0.5704</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>2.6386</v>
       </c>
       <c r="K14" t="n">
-        <v>125</v>
+        <v>177</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="M14" t="n">
-        <v>4.2138</v>
+        <v>3.209</v>
       </c>
       <c r="N14" t="n">
-        <v>125</v>
+        <v>339</v>
       </c>
     </row>
     <row r="15">
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.0477</v>
+        <v>3.0818</v>
       </c>
       <c r="C15" t="n">
-        <v>1.668</v>
+        <v>1.6867</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7632</v>
+        <v>0.7628</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0477</v>
+        <v>3.0818</v>
       </c>
       <c r="F15" t="n">
         <v>2.5536</v>
@@ -1136,139 +1136,139 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sense</t>
+          <t>b1t</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.7924</v>
+        <v>3.0518</v>
       </c>
       <c r="C16" t="n">
-        <v>1.5283</v>
+        <v>1.6702</v>
       </c>
       <c r="D16" t="n">
-        <v>0.647</v>
+        <v>0.7494</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7924</v>
+        <v>3.0518</v>
       </c>
       <c r="F16" t="n">
-        <v>2.7924</v>
+        <v>2.6018</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3.3867</v>
+        <v>2.9696</v>
       </c>
       <c r="I16" t="n">
-        <v>3.3867</v>
+        <v>2.9696</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3867</v>
+        <v>2.9696</v>
       </c>
       <c r="N16" t="n">
-        <v>109</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>jL</t>
+          <t>sense</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.726</v>
+        <v>3.0068</v>
       </c>
       <c r="C17" t="n">
-        <v>1.4919</v>
+        <v>1.6456</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6167</v>
+        <v>0.7292999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>2.726</v>
+        <v>3.0068</v>
       </c>
       <c r="F17" t="n">
-        <v>2.726</v>
+        <v>2.7921</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>3.2414</v>
+        <v>3.3862</v>
       </c>
       <c r="I17" t="n">
-        <v>3.2414</v>
+        <v>3.3862</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>144</v>
+        <v>109</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2414</v>
+        <v>3.3862</v>
       </c>
       <c r="N17" t="n">
-        <v>144</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>sdy</t>
+          <t>jL</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.7184</v>
+        <v>2.9901</v>
       </c>
       <c r="C18" t="n">
-        <v>1.4878</v>
+        <v>1.6365</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6133</v>
+        <v>0.7218</v>
       </c>
       <c r="E18" t="n">
-        <v>2.7184</v>
+        <v>2.9901</v>
       </c>
       <c r="F18" t="n">
-        <v>2.7184</v>
+        <v>2.726</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>3.2249</v>
+        <v>3.2414</v>
       </c>
       <c r="I18" t="n">
-        <v>3.308</v>
+        <v>3.2414</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>181</v>
+        <v>144</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.308</v>
+        <v>3.2414</v>
       </c>
       <c r="N18" t="n">
-        <v>181</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19">
@@ -1278,16 +1278,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.7126</v>
+        <v>2.8549</v>
       </c>
       <c r="C19" t="n">
-        <v>1.4846</v>
+        <v>1.5625</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6106</v>
+        <v>0.6614</v>
       </c>
       <c r="E19" t="n">
-        <v>2.7126</v>
+        <v>2.8549</v>
       </c>
       <c r="F19" t="n">
         <v>2.7126</v>
@@ -1320,139 +1320,139 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>KaiR0N-</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.6156</v>
+        <v>2.7318</v>
       </c>
       <c r="C20" t="n">
-        <v>1.4315</v>
+        <v>1.4951</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5665</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>2.6156</v>
+        <v>2.7318</v>
       </c>
       <c r="F20" t="n">
-        <v>2.5848</v>
+        <v>2.8042</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0308</v>
+        <v>-0.2184</v>
       </c>
       <c r="H20" t="n">
-        <v>3.6339</v>
+        <v>3.4127</v>
       </c>
       <c r="I20" t="n">
-        <v>1.9623</v>
+        <v>3.5006</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0308</v>
+        <v>-0.2184</v>
       </c>
       <c r="K20" t="n">
-        <v>107</v>
+        <v>150</v>
       </c>
       <c r="L20" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="M20" t="n">
-        <v>1.9931</v>
+        <v>3.2822</v>
       </c>
       <c r="N20" t="n">
-        <v>144</v>
+        <v>193</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>b1t</t>
+          <t>sdy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.6018</v>
+        <v>2.7282</v>
       </c>
       <c r="C21" t="n">
-        <v>1.424</v>
+        <v>1.4931</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5602</v>
+        <v>0.6048</v>
       </c>
       <c r="E21" t="n">
-        <v>2.6018</v>
+        <v>2.7282</v>
       </c>
       <c r="F21" t="n">
-        <v>2.6018</v>
+        <v>2.7184</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2.9696</v>
+        <v>3.2249</v>
       </c>
       <c r="I21" t="n">
-        <v>2.9696</v>
+        <v>3.308</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>144</v>
+        <v>181</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2.9696</v>
+        <v>3.308</v>
       </c>
       <c r="N21" t="n">
-        <v>144</v>
+        <v>181</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>KaiR0N-</t>
+          <t>br0</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.5858</v>
+        <v>2.5749</v>
       </c>
       <c r="C22" t="n">
-        <v>1.4152</v>
+        <v>1.4092</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5528999999999999</v>
+        <v>0.5363</v>
       </c>
       <c r="E22" t="n">
-        <v>2.5858</v>
+        <v>2.5749</v>
       </c>
       <c r="F22" t="n">
-        <v>2.8042</v>
+        <v>2.425</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2184</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>3.4127</v>
+        <v>2.5826</v>
       </c>
       <c r="I22" t="n">
-        <v>3.5006</v>
+        <v>2.6492</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2184</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>150</v>
+        <v>181</v>
       </c>
       <c r="L22" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2822</v>
+        <v>2.6492</v>
       </c>
       <c r="N22" t="n">
-        <v>193</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23">
@@ -1462,16 +1462,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.5417</v>
+        <v>2.5659</v>
       </c>
       <c r="C23" t="n">
-        <v>1.3911</v>
+        <v>1.4043</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5328000000000001</v>
+        <v>0.5323</v>
       </c>
       <c r="E23" t="n">
-        <v>2.5417</v>
+        <v>2.5659</v>
       </c>
       <c r="F23" t="n">
         <v>2.5417</v>
@@ -1504,139 +1504,139 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.5022</v>
+        <v>2.5162</v>
       </c>
       <c r="C24" t="n">
-        <v>1.3694</v>
+        <v>1.3771</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5148</v>
+        <v>0.5101</v>
       </c>
       <c r="E24" t="n">
-        <v>2.5022</v>
+        <v>2.5162</v>
       </c>
       <c r="F24" t="n">
-        <v>2.8767</v>
+        <v>2.5848</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.3745</v>
+        <v>0.0308</v>
       </c>
       <c r="H24" t="n">
-        <v>4.5971</v>
+        <v>3.6339</v>
       </c>
       <c r="I24" t="n">
-        <v>2.4824</v>
+        <v>1.9623</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.3745</v>
+        <v>0.0308</v>
       </c>
       <c r="K24" t="n">
-        <v>157</v>
+        <v>107</v>
       </c>
       <c r="L24" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M24" t="n">
-        <v>2.1079</v>
+        <v>1.9931</v>
       </c>
       <c r="N24" t="n">
-        <v>196</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>hallzerk</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.4314</v>
+        <v>2.4626</v>
       </c>
       <c r="C25" t="n">
-        <v>1.3307</v>
+        <v>1.3478</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4826</v>
+        <v>0.4862</v>
       </c>
       <c r="E25" t="n">
-        <v>2.4314</v>
+        <v>2.4626</v>
       </c>
       <c r="F25" t="n">
-        <v>1.3786</v>
+        <v>2.8767</v>
       </c>
       <c r="G25" t="n">
-        <v>1.0528</v>
+        <v>-0.3745</v>
       </c>
       <c r="H25" t="n">
-        <v>1.3786</v>
+        <v>4.5971</v>
       </c>
       <c r="I25" t="n">
-        <v>1.4506</v>
+        <v>2.4824</v>
       </c>
       <c r="J25" t="n">
-        <v>1.0528</v>
+        <v>-0.3745</v>
       </c>
       <c r="K25" t="n">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="L25" t="n">
-        <v>162</v>
+        <v>39</v>
       </c>
       <c r="M25" t="n">
-        <v>2.5034</v>
+        <v>2.1079</v>
       </c>
       <c r="N25" t="n">
-        <v>339</v>
+        <v>196</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>br0</t>
+          <t>hallzerk</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.425</v>
+        <v>2.4298</v>
       </c>
       <c r="C26" t="n">
-        <v>1.3272</v>
+        <v>1.3298</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4797</v>
+        <v>0.4715</v>
       </c>
       <c r="E26" t="n">
-        <v>2.425</v>
+        <v>2.4298</v>
       </c>
       <c r="F26" t="n">
-        <v>2.425</v>
+        <v>1.3783</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1.0528</v>
       </c>
       <c r="H26" t="n">
-        <v>2.5826</v>
+        <v>1.3783</v>
       </c>
       <c r="I26" t="n">
-        <v>2.6492</v>
+        <v>1.4503</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1.0528</v>
       </c>
       <c r="K26" t="n">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="M26" t="n">
-        <v>2.6492</v>
+        <v>2.5031</v>
       </c>
       <c r="N26" t="n">
-        <v>181</v>
+        <v>339</v>
       </c>
     </row>
     <row r="27">
@@ -1646,16 +1646,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.1571</v>
+        <v>2.2131</v>
       </c>
       <c r="C27" t="n">
-        <v>1.1806</v>
+        <v>1.2112</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3578</v>
+        <v>0.3747</v>
       </c>
       <c r="E27" t="n">
-        <v>2.1571</v>
+        <v>2.2131</v>
       </c>
       <c r="F27" t="n">
         <v>3.1018</v>
@@ -1688,139 +1688,139 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>acoR</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.1452</v>
+        <v>2.1981</v>
       </c>
       <c r="C28" t="n">
-        <v>1.1741</v>
+        <v>1.203</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3523</v>
+        <v>0.368</v>
       </c>
       <c r="E28" t="n">
-        <v>2.1452</v>
+        <v>2.1981</v>
       </c>
       <c r="F28" t="n">
-        <v>2.1452</v>
+        <v>2.1329</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>2.1452</v>
+        <v>2.1329</v>
       </c>
       <c r="I28" t="n">
-        <v>2.1452</v>
+        <v>2.1879</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>151</v>
+        <v>185</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>2.1452</v>
+        <v>2.1879</v>
       </c>
       <c r="N28" t="n">
-        <v>151</v>
+        <v>185</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>acoR</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.1329</v>
+        <v>2.1408</v>
       </c>
       <c r="C29" t="n">
-        <v>1.1673</v>
+        <v>1.1717</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3467</v>
+        <v>0.3424</v>
       </c>
       <c r="E29" t="n">
-        <v>2.1329</v>
+        <v>2.1408</v>
       </c>
       <c r="F29" t="n">
-        <v>2.1329</v>
+        <v>2.1452</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2.1329</v>
+        <v>2.1452</v>
       </c>
       <c r="I29" t="n">
-        <v>2.1879</v>
+        <v>2.1452</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>185</v>
+        <v>151</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>2.1879</v>
+        <v>2.1452</v>
       </c>
       <c r="N29" t="n">
-        <v>185</v>
+        <v>151</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Nexius</t>
+          <t>malta</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.0206</v>
+        <v>2.0798</v>
       </c>
       <c r="C30" t="n">
-        <v>1.1059</v>
+        <v>1.1383</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2956</v>
+        <v>0.3152</v>
       </c>
       <c r="E30" t="n">
-        <v>2.0206</v>
+        <v>2.0798</v>
       </c>
       <c r="F30" t="n">
-        <v>2.5386</v>
+        <v>1.2747</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.518</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>3.4815</v>
+        <v>1.2747</v>
       </c>
       <c r="I30" t="n">
-        <v>1.88</v>
+        <v>1.2747</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.518</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>157</v>
+        <v>57</v>
       </c>
       <c r="L30" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.362</v>
+        <v>1.2747</v>
       </c>
       <c r="N30" t="n">
-        <v>196</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31">
@@ -1830,16 +1830,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.0021</v>
+        <v>2.0451</v>
       </c>
       <c r="C31" t="n">
-        <v>1.0957</v>
+        <v>1.1193</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2872</v>
+        <v>0.2997</v>
       </c>
       <c r="E31" t="n">
-        <v>2.0021</v>
+        <v>2.0451</v>
       </c>
       <c r="F31" t="n">
         <v>2.935</v>
@@ -1872,219 +1872,219 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>mezii</t>
+          <t>Nexius</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.7022</v>
+        <v>1.9828</v>
       </c>
       <c r="C32" t="n">
-        <v>0.9316</v>
+        <v>1.0852</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1507</v>
+        <v>0.2719</v>
       </c>
       <c r="E32" t="n">
-        <v>1.7022</v>
+        <v>1.9828</v>
       </c>
       <c r="F32" t="n">
-        <v>1.7022</v>
+        <v>2.5386</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-0.518</v>
       </c>
       <c r="H32" t="n">
-        <v>1.7022</v>
+        <v>3.4815</v>
       </c>
       <c r="I32" t="n">
-        <v>1.7022</v>
+        <v>1.88</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-0.518</v>
       </c>
       <c r="K32" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="M32" t="n">
-        <v>1.7022</v>
+        <v>1.362</v>
       </c>
       <c r="N32" t="n">
-        <v>151</v>
+        <v>196</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>INS</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.6083</v>
+        <v>1.7119</v>
       </c>
       <c r="C33" t="n">
-        <v>0.8802</v>
+        <v>0.9369</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1079</v>
+        <v>0.1508</v>
       </c>
       <c r="E33" t="n">
-        <v>1.6083</v>
+        <v>1.7119</v>
       </c>
       <c r="F33" t="n">
-        <v>1.6083</v>
+        <v>1.5605</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.6083</v>
+        <v>1.5605</v>
       </c>
       <c r="I33" t="n">
-        <v>1.6083</v>
+        <v>1.5605</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>109</v>
+        <v>66</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.6083</v>
+        <v>1.5605</v>
       </c>
       <c r="N33" t="n">
-        <v>109</v>
+        <v>66</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>INS</t>
+          <t>mezii</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.5605</v>
+        <v>1.7035</v>
       </c>
       <c r="C34" t="n">
-        <v>0.8541</v>
+        <v>0.9323</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0862</v>
+        <v>0.1471</v>
       </c>
       <c r="E34" t="n">
-        <v>1.5605</v>
+        <v>1.7035</v>
       </c>
       <c r="F34" t="n">
-        <v>1.5605</v>
+        <v>1.7022</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1.5605</v>
+        <v>1.7022</v>
       </c>
       <c r="I34" t="n">
-        <v>1.5605</v>
+        <v>1.7022</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>66</v>
+        <v>151</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.5605</v>
+        <v>1.7022</v>
       </c>
       <c r="N34" t="n">
-        <v>66</v>
+        <v>151</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.4909</v>
+        <v>1.6151</v>
       </c>
       <c r="C35" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8839</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0545</v>
+        <v>0.1076</v>
       </c>
       <c r="E35" t="n">
-        <v>1.4909</v>
+        <v>1.6151</v>
       </c>
       <c r="F35" t="n">
-        <v>1.8318</v>
+        <v>1.6336</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.3409</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.8318</v>
+        <v>1.6336</v>
       </c>
       <c r="I35" t="n">
-        <v>1.8318</v>
+        <v>1.6336</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.3409</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="L35" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1.4909</v>
+        <v>1.6336</v>
       </c>
       <c r="N35" t="n">
-        <v>162</v>
+        <v>109</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>dycha</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.4698</v>
+        <v>1.5612</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8044</v>
+        <v>0.8544</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0449</v>
+        <v>0.0835</v>
       </c>
       <c r="E36" t="n">
-        <v>1.4698</v>
+        <v>1.5612</v>
       </c>
       <c r="F36" t="n">
-        <v>1.1045</v>
+        <v>1.8318</v>
       </c>
       <c r="G36" t="n">
-        <v>0.3653</v>
+        <v>-0.3409</v>
       </c>
       <c r="H36" t="n">
-        <v>1.1045</v>
+        <v>1.8318</v>
       </c>
       <c r="I36" t="n">
-        <v>1.1045</v>
+        <v>1.8318</v>
       </c>
       <c r="J36" t="n">
-        <v>0.3653</v>
+        <v>-0.3409</v>
       </c>
       <c r="K36" t="n">
         <v>131</v>
@@ -2093,7 +2093,7 @@
         <v>31</v>
       </c>
       <c r="M36" t="n">
-        <v>1.4698</v>
+        <v>1.4909</v>
       </c>
       <c r="N36" t="n">
         <v>162</v>
@@ -2102,47 +2102,47 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>dycha</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.4629</v>
+        <v>1.512</v>
       </c>
       <c r="C37" t="n">
-        <v>0.8006</v>
+        <v>0.8275</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0417</v>
+        <v>0.0616</v>
       </c>
       <c r="E37" t="n">
-        <v>1.4629</v>
+        <v>1.512</v>
       </c>
       <c r="F37" t="n">
-        <v>1.4629</v>
+        <v>1.1045</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>0.3653</v>
       </c>
       <c r="H37" t="n">
-        <v>1.4629</v>
+        <v>1.1045</v>
       </c>
       <c r="I37" t="n">
-        <v>1.5006</v>
+        <v>1.1045</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>0.3653</v>
       </c>
       <c r="K37" t="n">
-        <v>185</v>
+        <v>131</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="M37" t="n">
-        <v>1.5006</v>
+        <v>1.4698</v>
       </c>
       <c r="N37" t="n">
-        <v>185</v>
+        <v>162</v>
       </c>
     </row>
     <row r="38">
@@ -2152,16 +2152,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.3581</v>
+        <v>1.4212</v>
       </c>
       <c r="C38" t="n">
-        <v>0.7433</v>
+        <v>0.7778</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.006</v>
+        <v>0.021</v>
       </c>
       <c r="E38" t="n">
-        <v>1.3581</v>
+        <v>1.4212</v>
       </c>
       <c r="F38" t="n">
         <v>1.3581</v>
@@ -2194,369 +2194,369 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>ADDICT</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.3238</v>
+        <v>1.4033</v>
       </c>
       <c r="C39" t="n">
-        <v>0.7245</v>
+        <v>0.768</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.0216</v>
+        <v>0.013</v>
       </c>
       <c r="E39" t="n">
-        <v>1.3238</v>
+        <v>1.4033</v>
       </c>
       <c r="F39" t="n">
-        <v>1.3238</v>
+        <v>1.0801</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1.3238</v>
+        <v>1.0801</v>
       </c>
       <c r="I39" t="n">
-        <v>1.3238</v>
+        <v>1.0801</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>125</v>
+        <v>57</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1.3238</v>
+        <v>1.0801</v>
       </c>
       <c r="N39" t="n">
-        <v>125</v>
+        <v>57</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>malta</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.2747</v>
+        <v>1.3832</v>
       </c>
       <c r="C40" t="n">
-        <v>0.6976</v>
+        <v>0.757</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.0439</v>
+        <v>0.004</v>
       </c>
       <c r="E40" t="n">
-        <v>1.2747</v>
+        <v>1.3832</v>
       </c>
       <c r="F40" t="n">
-        <v>1.2747</v>
+        <v>1.4629</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1.2747</v>
+        <v>1.4629</v>
       </c>
       <c r="I40" t="n">
-        <v>1.2747</v>
+        <v>1.5006</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>57</v>
+        <v>185</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.2747</v>
+        <v>1.5006</v>
       </c>
       <c r="N40" t="n">
-        <v>57</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>afro</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.2573</v>
+        <v>1.2696</v>
       </c>
       <c r="C41" t="n">
-        <v>0.6881</v>
+        <v>0.6948</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.0519</v>
+        <v>-0.0467</v>
       </c>
       <c r="E41" t="n">
-        <v>1.2573</v>
+        <v>1.2696</v>
       </c>
       <c r="F41" t="n">
-        <v>1.2573</v>
+        <v>1.3238</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1.2573</v>
+        <v>1.3238</v>
       </c>
       <c r="I41" t="n">
-        <v>1.2573</v>
+        <v>1.3238</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>151</v>
+        <v>125</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1.2573</v>
+        <v>1.3238</v>
       </c>
       <c r="N41" t="n">
-        <v>151</v>
+        <v>125</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ADDICT</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.0801</v>
+        <v>1.1329</v>
       </c>
       <c r="C42" t="n">
-        <v>0.5911</v>
+        <v>0.62</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.1325</v>
+        <v>-0.1078</v>
       </c>
       <c r="E42" t="n">
-        <v>1.0801</v>
+        <v>1.1329</v>
       </c>
       <c r="F42" t="n">
-        <v>1.0801</v>
+        <v>0.9905</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1.0801</v>
+        <v>0.9905</v>
       </c>
       <c r="I42" t="n">
-        <v>1.0801</v>
+        <v>0.9905</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1.0801</v>
+        <v>0.9905</v>
       </c>
       <c r="N42" t="n">
-        <v>57</v>
+        <v>105</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>afro</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.0127</v>
+        <v>1.1112</v>
       </c>
       <c r="C43" t="n">
-        <v>0.5542</v>
+        <v>0.6082</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.1632</v>
+        <v>-0.1175</v>
       </c>
       <c r="E43" t="n">
-        <v>1.0127</v>
+        <v>1.1112</v>
       </c>
       <c r="F43" t="n">
-        <v>1.0127</v>
+        <v>1.2573</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1.0127</v>
+        <v>1.2573</v>
       </c>
       <c r="I43" t="n">
-        <v>1.0127</v>
+        <v>1.2573</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1.0127</v>
+        <v>1.2573</v>
       </c>
       <c r="N43" t="n">
-        <v>125</v>
+        <v>151</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>aliStair</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.9905</v>
+        <v>1.0329</v>
       </c>
       <c r="C44" t="n">
-        <v>0.5421</v>
+        <v>0.5653</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.1733</v>
+        <v>-0.1524</v>
       </c>
       <c r="E44" t="n">
-        <v>0.9905</v>
+        <v>1.0329</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9905</v>
+        <v>0.8855</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.9905</v>
+        <v>0.8855</v>
       </c>
       <c r="I44" t="n">
-        <v>0.9905</v>
+        <v>0.8855</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.9905</v>
+        <v>0.8855</v>
       </c>
       <c r="N44" t="n">
-        <v>105</v>
+        <v>66</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>aliStair</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8855</v>
+        <v>0.9937</v>
       </c>
       <c r="C45" t="n">
-        <v>0.4846</v>
+        <v>0.5438</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2211</v>
+        <v>-0.17</v>
       </c>
       <c r="E45" t="n">
-        <v>0.8855</v>
+        <v>0.9937</v>
       </c>
       <c r="F45" t="n">
-        <v>0.8855</v>
+        <v>1.0127</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.8855</v>
+        <v>1.0127</v>
       </c>
       <c r="I45" t="n">
-        <v>0.8855</v>
+        <v>1.0127</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>66</v>
+        <v>125</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.8855</v>
+        <v>1.0127</v>
       </c>
       <c r="N45" t="n">
-        <v>66</v>
+        <v>125</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CacaNito</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8159</v>
+        <v>0.9388</v>
       </c>
       <c r="C46" t="n">
-        <v>0.4465</v>
+        <v>0.5138</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.2528</v>
+        <v>-0.1945</v>
       </c>
       <c r="E46" t="n">
-        <v>0.8159</v>
+        <v>0.9388</v>
       </c>
       <c r="F46" t="n">
-        <v>0.8159</v>
+        <v>0.7276</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.8159</v>
+        <v>0.7276</v>
       </c>
       <c r="I46" t="n">
-        <v>0.8159</v>
+        <v>0.7276</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.8159</v>
+        <v>0.7276</v>
       </c>
       <c r="N46" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="47">
@@ -2566,16 +2566,16 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7633</v>
+        <v>0.7728</v>
       </c>
       <c r="C47" t="n">
-        <v>0.4178</v>
+        <v>0.423</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.2767</v>
+        <v>-0.2686</v>
       </c>
       <c r="E47" t="n">
-        <v>0.7633</v>
+        <v>0.7728</v>
       </c>
       <c r="F47" t="n">
         <v>1.6815</v>
@@ -2608,47 +2608,47 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>CacaNito</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7276</v>
+        <v>0.7608</v>
       </c>
       <c r="C48" t="n">
-        <v>0.3982</v>
+        <v>0.4164</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.293</v>
+        <v>-0.274</v>
       </c>
       <c r="E48" t="n">
-        <v>0.7276</v>
+        <v>0.7608</v>
       </c>
       <c r="F48" t="n">
-        <v>0.7276</v>
+        <v>0.8157</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.7276</v>
+        <v>0.8157</v>
       </c>
       <c r="I48" t="n">
-        <v>0.7276</v>
+        <v>0.8157</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.7276</v>
+        <v>0.8157</v>
       </c>
       <c r="N48" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="49">
@@ -2658,16 +2658,16 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.751</v>
       </c>
       <c r="C49" t="n">
-        <v>0.3765</v>
+        <v>0.411</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.311</v>
+        <v>-0.2784</v>
       </c>
       <c r="E49" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.751</v>
       </c>
       <c r="F49" t="n">
         <v>0.6879999999999999</v>
@@ -2704,28 +2704,28 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6902</v>
       </c>
       <c r="C50" t="n">
-        <v>0.3738</v>
+        <v>0.3777</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3133</v>
+        <v>-0.3055</v>
       </c>
       <c r="E50" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6902</v>
       </c>
       <c r="F50" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6832</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6832</v>
       </c>
       <c r="I50" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6832</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -2737,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.6832</v>
       </c>
       <c r="N50" t="n">
         <v>64</v>
@@ -2746,369 +2746,369 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S1ren</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6544</v>
+        <v>0.6798</v>
       </c>
       <c r="C51" t="n">
-        <v>0.3582</v>
+        <v>0.3721</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.3263</v>
+        <v>-0.3102</v>
       </c>
       <c r="E51" t="n">
-        <v>0.6544</v>
+        <v>0.6798</v>
       </c>
       <c r="F51" t="n">
-        <v>0.5427</v>
+        <v>0.491</v>
       </c>
       <c r="G51" t="n">
-        <v>0.1117</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.5427</v>
+        <v>0.491</v>
       </c>
       <c r="I51" t="n">
-        <v>0.5567</v>
+        <v>0.491</v>
       </c>
       <c r="J51" t="n">
-        <v>0.1117</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>150</v>
+        <v>64</v>
       </c>
       <c r="L51" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.6684</v>
+        <v>0.491</v>
       </c>
       <c r="N51" t="n">
-        <v>193</v>
+        <v>64</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>S1ren</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.4905</v>
+        <v>0.6044</v>
       </c>
       <c r="C52" t="n">
-        <v>0.2684</v>
+        <v>0.3308</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.4009</v>
+        <v>-0.3438</v>
       </c>
       <c r="E52" t="n">
-        <v>0.4905</v>
+        <v>0.6044</v>
       </c>
       <c r="F52" t="n">
-        <v>0.4905</v>
+        <v>0.5427</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>0.1117</v>
       </c>
       <c r="H52" t="n">
-        <v>0.4905</v>
+        <v>0.5427</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4905</v>
+        <v>0.5567</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>0.1117</v>
       </c>
       <c r="K52" t="n">
-        <v>64</v>
+        <v>150</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M52" t="n">
-        <v>0.4905</v>
+        <v>0.6684</v>
       </c>
       <c r="N52" t="n">
-        <v>64</v>
+        <v>193</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.3855</v>
+        <v>0.3474</v>
       </c>
       <c r="C53" t="n">
-        <v>0.211</v>
+        <v>0.1901</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4487</v>
+        <v>-0.4586</v>
       </c>
       <c r="E53" t="n">
-        <v>0.3855</v>
+        <v>0.3474</v>
       </c>
       <c r="F53" t="n">
-        <v>0.9774</v>
+        <v>0.3403</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.5919</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.9774</v>
+        <v>0.3403</v>
       </c>
       <c r="I53" t="n">
-        <v>0.9774</v>
+        <v>0.3403</v>
       </c>
       <c r="J53" t="n">
-        <v>-0.5919</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="L53" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0.3855000000000001</v>
+        <v>0.3403</v>
       </c>
       <c r="N53" t="n">
-        <v>162</v>
+        <v>105</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Westmelon</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.3832</v>
+        <v>0.3116</v>
       </c>
       <c r="C54" t="n">
-        <v>0.2097</v>
+        <v>0.1705</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4498</v>
+        <v>-0.4746</v>
       </c>
       <c r="E54" t="n">
-        <v>0.3832</v>
+        <v>0.3116</v>
       </c>
       <c r="F54" t="n">
-        <v>0.3832</v>
+        <v>0.9774</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>-0.5919</v>
       </c>
       <c r="H54" t="n">
-        <v>0.3832</v>
+        <v>0.9774</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3832</v>
+        <v>0.9774</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>-0.5919</v>
       </c>
       <c r="K54" t="n">
-        <v>64</v>
+        <v>131</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="M54" t="n">
-        <v>0.3832</v>
+        <v>0.3855000000000001</v>
       </c>
       <c r="N54" t="n">
-        <v>64</v>
+        <v>162</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>nawwk</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.3403</v>
+        <v>0.2195</v>
       </c>
       <c r="C55" t="n">
-        <v>0.1862</v>
+        <v>0.1201</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.4693</v>
+        <v>-0.5158</v>
       </c>
       <c r="E55" t="n">
-        <v>0.3403</v>
+        <v>0.2195</v>
       </c>
       <c r="F55" t="n">
-        <v>0.3403</v>
+        <v>0.2276</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.3403</v>
+        <v>0.2276</v>
       </c>
       <c r="I55" t="n">
-        <v>0.3403</v>
+        <v>0.2276</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.3403</v>
+        <v>0.2276</v>
       </c>
       <c r="N55" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>Westmelon</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.2408</v>
+        <v>0.1886</v>
       </c>
       <c r="C56" t="n">
-        <v>0.1318</v>
+        <v>0.1032</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.5296</v>
       </c>
       <c r="E56" t="n">
-        <v>0.2408</v>
+        <v>0.1886</v>
       </c>
       <c r="F56" t="n">
-        <v>0.2408</v>
+        <v>0.3692</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.2408</v>
+        <v>0.3692</v>
       </c>
       <c r="I56" t="n">
-        <v>0.2408</v>
+        <v>0.3692</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>125</v>
+        <v>64</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.2408</v>
+        <v>0.3692</v>
       </c>
       <c r="N56" t="n">
-        <v>125</v>
+        <v>64</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>nawwk</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.2279</v>
+        <v>0.1086</v>
       </c>
       <c r="C57" t="n">
-        <v>0.1247</v>
+        <v>0.0594</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5205</v>
+        <v>-0.5653</v>
       </c>
       <c r="E57" t="n">
-        <v>0.2279</v>
+        <v>0.1086</v>
       </c>
       <c r="F57" t="n">
-        <v>0.2279</v>
+        <v>0.2515</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>-0.0467</v>
       </c>
       <c r="H57" t="n">
-        <v>0.2279</v>
+        <v>0.2515</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2279</v>
+        <v>0.1358</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>-0.0467</v>
       </c>
       <c r="K57" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M57" t="n">
-        <v>0.2279</v>
+        <v>0.08910000000000001</v>
       </c>
       <c r="N57" t="n">
-        <v>109</v>
+        <v>144</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.2048</v>
+        <v>0.0761</v>
       </c>
       <c r="C58" t="n">
-        <v>0.1121</v>
+        <v>0.0416</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.531</v>
+        <v>-0.5798</v>
       </c>
       <c r="E58" t="n">
-        <v>0.2048</v>
+        <v>0.0761</v>
       </c>
       <c r="F58" t="n">
-        <v>0.2515</v>
+        <v>0.2408</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.0467</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2515</v>
+        <v>0.2408</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1358</v>
+        <v>0.2408</v>
       </c>
       <c r="J58" t="n">
-        <v>-0.0467</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="L58" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0.08910000000000001</v>
+        <v>0.2408</v>
       </c>
       <c r="N58" t="n">
-        <v>144</v>
+        <v>125</v>
       </c>
     </row>
     <row r="59">
@@ -3118,16 +3118,16 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.0477</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="C59" t="n">
-        <v>0.0261</v>
+        <v>0.0407</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6025</v>
+        <v>-0.5806</v>
       </c>
       <c r="E59" t="n">
-        <v>0.0477</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="F59" t="n">
         <v>0.0477</v>
@@ -3164,16 +3164,16 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.0626</v>
+        <v>-0.1905</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.0343</v>
+        <v>-0.1043</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6526999999999999</v>
+        <v>-0.6989</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.0626</v>
+        <v>-0.1905</v>
       </c>
       <c r="F60" t="n">
         <v>-0.0759</v>
@@ -3210,16 +3210,16 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.2322</v>
+        <v>-0.2283</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.1271</v>
+        <v>-0.1249</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7299</v>
+        <v>-0.7158</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.2322</v>
+        <v>-0.2283</v>
       </c>
       <c r="F61" t="n">
         <v>-0.2322</v>
@@ -3256,16 +3256,16 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.3188</v>
+        <v>-0.4089</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.1745</v>
+        <v>-0.2238</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.7693</v>
+        <v>-0.7965</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.3188</v>
+        <v>-0.4089</v>
       </c>
       <c r="F62" t="n">
         <v>-0.3188</v>
@@ -3298,93 +3298,93 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>EmiliaQAQ</t>
+          <t>Woro2k</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.3228</v>
+        <v>-0.4319</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.1767</v>
+        <v>-0.2364</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7711</v>
+        <v>-0.8067</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.3228</v>
+        <v>-0.4319</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.3228</v>
+        <v>-0.3901</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.3228</v>
+        <v>-0.3901</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.3228</v>
+        <v>-0.4002</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>64</v>
+        <v>181</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.3228</v>
+        <v>-0.4002</v>
       </c>
       <c r="N63" t="n">
-        <v>64</v>
+        <v>181</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Woro2k</t>
+          <t>EmiliaQAQ</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.3901</v>
+        <v>-0.5004</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.2135</v>
+        <v>-0.2739</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.8018</v>
+        <v>-0.8373</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.3901</v>
+        <v>-0.5004</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.3901</v>
+        <v>-0.3226</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.3901</v>
+        <v>-0.3226</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.4002</v>
+        <v>-0.3226</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>181</v>
+        <v>64</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.4002</v>
+        <v>-0.3226</v>
       </c>
       <c r="N64" t="n">
-        <v>181</v>
+        <v>64</v>
       </c>
     </row>
     <row r="65">
@@ -3394,28 +3394,28 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.5581</v>
+        <v>-0.5458</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.3054</v>
+        <v>-0.2987</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8783</v>
+        <v>-0.8576</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.5581</v>
+        <v>-0.5458</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.5581</v>
+        <v>-0.5586</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.5581</v>
+        <v>-0.5586</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.5581</v>
+        <v>-0.5586</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -3427,7 +3427,7 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.5581</v>
+        <v>-0.5586</v>
       </c>
       <c r="N65" t="n">
         <v>109</v>
@@ -3440,16 +3440,16 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.7149</v>
+        <v>-0.7976</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.3913</v>
+        <v>-0.4365</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.9496</v>
+        <v>-0.9701</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.7149</v>
+        <v>-0.7976</v>
       </c>
       <c r="F66" t="n">
         <v>-0.153</v>
@@ -3486,16 +3486,16 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.8065</v>
+        <v>-0.9542</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.4414</v>
+        <v>-0.5222</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.9913</v>
+        <v>-1.04</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.8065</v>
+        <v>-0.9542</v>
       </c>
       <c r="F67" t="n">
         <v>-0.8065</v>
@@ -3528,47 +3528,47 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>roeJ</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.8158</v>
+        <v>-0.9858</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.4465</v>
+        <v>-0.5395</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9956</v>
+        <v>-1.0542</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.8158</v>
+        <v>-0.9858</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.8158</v>
+        <v>-0.9737</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.8158</v>
+        <v>-0.9737</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.8158</v>
+        <v>-0.9737</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>105</v>
+        <v>151</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.8158</v>
+        <v>-0.9737</v>
       </c>
       <c r="N68" t="n">
-        <v>105</v>
+        <v>151</v>
       </c>
     </row>
     <row r="69">
@@ -3578,16 +3578,16 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.882</v>
+        <v>-1.0408</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.4827</v>
+        <v>-0.5696</v>
       </c>
       <c r="D69" t="n">
-        <v>-1.0257</v>
+        <v>-1.0787</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.882</v>
+        <v>-1.0408</v>
       </c>
       <c r="F69" t="n">
         <v>-0.882</v>
@@ -3620,139 +3620,139 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.8825</v>
+        <v>-1.0555</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.483</v>
+        <v>-0.5777</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.0259</v>
+        <v>-1.0853</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.8825</v>
+        <v>-1.0555</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.7734</v>
+        <v>-0.8158</v>
       </c>
       <c r="G70" t="n">
-        <v>0.8909</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-1.7734</v>
+        <v>-0.8158</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.9141</v>
+        <v>-0.8158</v>
       </c>
       <c r="J70" t="n">
-        <v>0.8909</v>
+        <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>229</v>
+        <v>105</v>
       </c>
       <c r="L70" t="n">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-1.0232</v>
+        <v>-0.8158</v>
       </c>
       <c r="N70" t="n">
-        <v>381</v>
+        <v>105</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sico</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.9556</v>
+        <v>-1.1099</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.523</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.0592</v>
+        <v>-1.1096</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.9556</v>
+        <v>-1.1099</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.9556</v>
+        <v>-1.7734</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>0.8909</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.9556</v>
+        <v>-1.7734</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.9556</v>
+        <v>-1.9141</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>0.8909</v>
       </c>
       <c r="K71" t="n">
-        <v>66</v>
+        <v>229</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.9556</v>
+        <v>-1.0232</v>
       </c>
       <c r="N71" t="n">
-        <v>66</v>
+        <v>381</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>roeJ</t>
+          <t>Sico</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.9737</v>
+        <v>-1.1466</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.5329</v>
+        <v>-0.6274999999999999</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.0675</v>
+        <v>-1.126</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.9737</v>
+        <v>-1.1466</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.9737</v>
+        <v>-0.9556</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.9737</v>
+        <v>-0.9556</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.9737</v>
+        <v>-0.9556</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.9737</v>
+        <v>-0.9556</v>
       </c>
       <c r="N72" t="n">
-        <v>151</v>
+        <v>66</v>
       </c>
     </row>
     <row r="73">
@@ -3762,28 +3762,28 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.0027</v>
+        <v>-1.181</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.5488</v>
+        <v>-0.6464</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0807</v>
+        <v>-1.1413</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.0027</v>
+        <v>-1.181</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.0027</v>
+        <v>-1.0026</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.0027</v>
+        <v>-1.0026</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.0027</v>
+        <v>-1.0026</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -3795,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-1.0027</v>
+        <v>-1.0026</v>
       </c>
       <c r="N73" t="n">
         <v>64</v>
@@ -3808,16 +3808,16 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.0218</v>
+        <v>-1.1985</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.5592</v>
+        <v>-0.6559</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.0893</v>
+        <v>-1.1492</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.0218</v>
+        <v>-1.1985</v>
       </c>
       <c r="F74" t="n">
         <v>-1.0218</v>
@@ -3850,124 +3850,124 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Vexite</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.2862</v>
+        <v>-1.5266</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.7039</v>
+        <v>-0.8355</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.2097</v>
+        <v>-1.2957</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.2862</v>
+        <v>-1.5266</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.2862</v>
+        <v>-0.5315</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.2862</v>
+        <v>-0.5315</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.2862</v>
+        <v>-0.5315</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K75" t="n">
-        <v>66</v>
+        <v>131</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.2862</v>
+        <v>-1.5315</v>
       </c>
       <c r="N75" t="n">
-        <v>66</v>
+        <v>162</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>hazr</t>
+          <t>Vexite</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.338</v>
+        <v>-1.6634</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.7323</v>
+        <v>-0.9104</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.2333</v>
+        <v>-1.3568</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.338</v>
+        <v>-1.6634</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.338</v>
+        <v>-1.2862</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.338</v>
+        <v>-1.2862</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.338</v>
+        <v>-1.2862</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.338</v>
+        <v>-1.2862</v>
       </c>
       <c r="N76" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BRACE</t>
+          <t>hazr</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.4246</v>
+        <v>-1.7549</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.7796999999999999</v>
+        <v>-0.9605</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.2727</v>
+        <v>-1.3977</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.4246</v>
+        <v>-1.7549</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.4246</v>
+        <v>-1.338</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.4246</v>
+        <v>-1.338</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.4246</v>
+        <v>-1.338</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -3979,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.4246</v>
+        <v>-1.338</v>
       </c>
       <c r="N77" t="n">
         <v>57</v>
@@ -3988,47 +3988,47 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>BRACE</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.5315</v>
+        <v>-1.9003</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.8381999999999999</v>
+        <v>-1.04</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.3214</v>
+        <v>-1.4626</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.5315</v>
+        <v>-1.9003</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.5315</v>
+        <v>-1.4246</v>
       </c>
       <c r="G78" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.5315</v>
+        <v>-1.4246</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.5315</v>
+        <v>-1.4246</v>
       </c>
       <c r="J78" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>131</v>
+        <v>57</v>
       </c>
       <c r="L78" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-1.5315</v>
+        <v>-1.4246</v>
       </c>
       <c r="N78" t="n">
-        <v>162</v>
+        <v>57</v>
       </c>
     </row>
     <row r="79">
@@ -4038,16 +4038,16 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.2241</v>
+        <v>-2.495</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.2172</v>
+        <v>-1.3655</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.6367</v>
+        <v>-1.7283</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.2241</v>
+        <v>-2.495</v>
       </c>
       <c r="F79" t="n">
         <v>-2.2241</v>
@@ -4084,16 +4084,16 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-3.1083</v>
+        <v>-3.4333</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.7012</v>
+        <v>-1.879</v>
       </c>
       <c r="D80" t="n">
-        <v>-2.0392</v>
+        <v>-2.1474</v>
       </c>
       <c r="E80" t="n">
-        <v>-3.1083</v>
+        <v>-3.4333</v>
       </c>
       <c r="F80" t="n">
         <v>-2.1852</v>
@@ -4130,16 +4130,16 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-3.3053</v>
+        <v>-3.9023</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.809</v>
+        <v>-2.1357</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.1288</v>
+        <v>-2.3569</v>
       </c>
       <c r="E81" t="n">
-        <v>-3.3053</v>
+        <v>-3.9023</v>
       </c>
       <c r="F81" t="n">
         <v>-3.3053</v>
@@ -7843,7 +7843,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -8003,7 +8003,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -8128,7 +8128,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -8168,7 +8168,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -8323,7 +8323,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -8363,7 +8363,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -8403,7 +8403,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -8568,7 +8568,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -9269,10 +9269,10 @@
         <v>1.7</v>
       </c>
       <c r="I127" t="n">
-        <v>1.3788</v>
+        <v>1.3782</v>
       </c>
       <c r="J127" t="n">
-        <v>39.9852</v>
+        <v>39.9678</v>
       </c>
     </row>
     <row r="128">
@@ -9306,13 +9306,13 @@
         <v>29</v>
       </c>
       <c r="H128" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I128" t="n">
-        <v>0.9550999999999999</v>
+        <v>0.9725</v>
       </c>
       <c r="J128" t="n">
-        <v>27.6979</v>
+        <v>28.2025</v>
       </c>
     </row>
     <row r="129">
@@ -9349,10 +9349,10 @@
         <v>1.16</v>
       </c>
       <c r="I129" t="n">
-        <v>0.46</v>
+        <v>0.4598</v>
       </c>
       <c r="J129" t="n">
-        <v>13.34</v>
+        <v>13.3342</v>
       </c>
     </row>
     <row r="130">
@@ -9389,10 +9389,10 @@
         <v>0.97</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1669</v>
+        <v>-0.1672</v>
       </c>
       <c r="J130" t="n">
-        <v>-4.8401</v>
+        <v>-4.8488</v>
       </c>
     </row>
     <row r="131">
@@ -9429,10 +9429,10 @@
         <v>0.64</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.9655</v>
+        <v>-0.9658</v>
       </c>
       <c r="J131" t="n">
-        <v>-27.9995</v>
+        <v>-28.0082</v>
       </c>
     </row>
     <row r="132">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -10288,7 +10288,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -10328,7 +10328,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -10483,7 +10483,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -10563,7 +10563,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10648,7 +10648,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -10688,7 +10688,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -10728,7 +10728,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -10768,7 +10768,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -10843,7 +10843,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10883,7 +10883,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10923,7 +10923,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10963,7 +10963,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -11003,7 +11003,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -11048,7 +11048,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -11128,7 +11128,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -11168,7 +11168,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -11208,7 +11208,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -11243,7 +11243,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11323,7 +11323,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11363,7 +11363,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11403,7 +11403,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -16669,10 +16669,10 @@
         <v>1.24</v>
       </c>
       <c r="I312" t="n">
-        <v>0.4958</v>
+        <v>0.4953</v>
       </c>
       <c r="J312" t="n">
-        <v>11.8992</v>
+        <v>11.8872</v>
       </c>
     </row>
     <row r="313">
@@ -16709,10 +16709,10 @@
         <v>1.21</v>
       </c>
       <c r="I313" t="n">
-        <v>0.4461</v>
+        <v>0.4456</v>
       </c>
       <c r="J313" t="n">
-        <v>10.7064</v>
+        <v>10.6944</v>
       </c>
     </row>
     <row r="314">
@@ -16749,10 +16749,10 @@
         <v>1.13</v>
       </c>
       <c r="I314" t="n">
-        <v>0.3058</v>
+        <v>0.3055</v>
       </c>
       <c r="J314" t="n">
-        <v>7.3392</v>
+        <v>7.332</v>
       </c>
     </row>
     <row r="315">
@@ -16786,13 +16786,13 @@
         <v>24</v>
       </c>
       <c r="H315" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="I315" t="n">
+        <v>-0.0011</v>
+      </c>
+      <c r="J315" t="n">
         <v>-0.0264</v>
-      </c>
-      <c r="J315" t="n">
-        <v>-0.6336000000000001</v>
       </c>
     </row>
     <row r="316">
@@ -16829,10 +16829,10 @@
         <v>0.53</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.499</v>
+        <v>-0.4992</v>
       </c>
       <c r="J316" t="n">
-        <v>-11.976</v>
+        <v>-11.9808</v>
       </c>
     </row>
     <row r="317">
@@ -18266,19 +18266,19 @@
         <v>24</v>
       </c>
       <c r="H352" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="I352" t="n">
-        <v>0.8321</v>
+        <v>0.8181</v>
       </c>
       <c r="J352" t="n">
-        <v>19.9704</v>
+        <v>19.6344</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -18309,10 +18309,10 @@
         <v>1.23</v>
       </c>
       <c r="I353" t="n">
-        <v>0.4784</v>
+        <v>0.4789</v>
       </c>
       <c r="J353" t="n">
-        <v>11.4816</v>
+        <v>11.4936</v>
       </c>
     </row>
     <row r="354">
@@ -18349,10 +18349,10 @@
         <v>0.93</v>
       </c>
       <c r="I354" t="n">
-        <v>-0.1135</v>
+        <v>-0.1133</v>
       </c>
       <c r="J354" t="n">
-        <v>-2.724</v>
+        <v>-2.7192</v>
       </c>
     </row>
     <row r="355">
@@ -18389,10 +18389,10 @@
         <v>0.79</v>
       </c>
       <c r="I355" t="n">
-        <v>-0.2645</v>
+        <v>-0.2643</v>
       </c>
       <c r="J355" t="n">
-        <v>-6.348</v>
+        <v>-6.3432</v>
       </c>
     </row>
     <row r="356">
@@ -18429,10 +18429,10 @@
         <v>0.71</v>
       </c>
       <c r="I356" t="n">
-        <v>-0.3405</v>
+        <v>-0.3404</v>
       </c>
       <c r="J356" t="n">
-        <v>-8.172000000000001</v>
+        <v>-8.169600000000001</v>
       </c>
     </row>
     <row r="357">
@@ -18638,7 +18638,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -21843,7 +21843,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -21883,7 +21883,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -21923,7 +21923,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -21963,7 +21963,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -22003,7 +22003,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -22048,7 +22048,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D447" t="n">
@@ -22088,7 +22088,7 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D448" t="n">
@@ -22128,7 +22128,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D449" t="n">
@@ -22168,7 +22168,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D450" t="n">
@@ -22208,7 +22208,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D451" t="n">
@@ -22243,7 +22243,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -22283,7 +22283,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -22323,7 +22323,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -22363,7 +22363,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -22403,7 +22403,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -22448,7 +22448,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D457" t="n">
@@ -22488,7 +22488,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D458" t="n">
@@ -22528,7 +22528,7 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D459" t="n">
@@ -22568,7 +22568,7 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D460" t="n">
@@ -22608,7 +22608,7 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D461" t="n">
@@ -26158,7 +26158,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -26648,7 +26648,7 @@
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D562" t="n">
@@ -26688,7 +26688,7 @@
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D563" t="n">
@@ -26728,7 +26728,7 @@
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D564" t="n">
@@ -26768,7 +26768,7 @@
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D565" t="n">
@@ -26808,7 +26808,7 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="D566" t="n">
@@ -26843,7 +26843,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
@@ -26883,7 +26883,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C568" t="inlineStr">
@@ -26923,7 +26923,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -26963,7 +26963,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -27003,7 +27003,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>BetBoom</t>
+          <t>BETBOOM</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
